--- a/1. data/Barkley-Sk_pre-smolt_abundances.xlsx
+++ b/1. data/Barkley-Sk_pre-smolt_abundances.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brownn\Documents\WCVI\Barkley-Sk-CSAS\1. data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45793E4F-63E2-43BF-B8B4-A5720D5BF6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3A6A23-78BD-405B-B0CD-A17B2BB718DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{93B9BABA-C468-4873-970E-7D7E9A90394F}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{93B9BABA-C468-4873-970E-7D7E9A90394F}"/>
   </bookViews>
   <sheets>
     <sheet name="ATS_estimates" sheetId="2" r:id="rId1"/>
@@ -46,6 +46,7 @@
     <author>Brown, Nicholas</author>
     <author>tc={9450F348-AFEB-4317-AD43-51976EFBA421}</author>
     <author>tc={C335BF2D-8A76-4A85-B639-EC939DD5E53A}</author>
+    <author>tc={3E6EE213-51C5-4BE7-94A1-C3C937E7343E}</author>
     <author>tc={288476D4-5EF1-4853-B334-5E56430540C8}</author>
     <author>tc={FC5C3F1C-3F41-443B-A044-4AEECF017EAF}</author>
     <author>tc={80809EA6-1C75-4782-B75F-9B8D8E1FF3DD}</author>
@@ -128,7 +129,15 @@
     1977-1985 average CV applied to guesstimated mean</t>
       </text>
     </comment>
-    <comment ref="G211" authorId="4" shapeId="0" xr:uid="{288476D4-5EF1-4853-B334-5E56430540C8}">
+    <comment ref="F211" authorId="4" shapeId="0" xr:uid="{3E6EE213-51C5-4BE7-94A1-C3C937E7343E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Assuming 50/50 Sk/Stickle. Tows caught 3 Sk, 6 Stickle, but notes indicate they likely hit a pocket of stickles at a shallower depth</t>
+      </text>
+    </comment>
+    <comment ref="G212" authorId="5" shapeId="0" xr:uid="{288476D4-5EF1-4853-B334-5E56430540C8}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -136,7 +145,7 @@
     Converts 95% CI of the total limnetic fish estimate to a coefficient of variation, and then multiplies that by the species specific estimate to yield and SD value. </t>
       </text>
     </comment>
-    <comment ref="I211" authorId="5" shapeId="0" xr:uid="{FC5C3F1C-3F41-443B-A044-4AEECF017EAF}">
+    <comment ref="I212" authorId="6" shapeId="0" xr:uid="{FC5C3F1C-3F41-443B-A044-4AEECF017EAF}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -144,7 +153,7 @@
     Converts 95% CI of the total limnetic fish estimate to a coefficient of variation, and then multiplies that by the species specific estimate to yield and SD value. </t>
       </text>
     </comment>
-    <comment ref="G212" authorId="6" shapeId="0" xr:uid="{80809EA6-1C75-4782-B75F-9B8D8E1FF3DD}">
+    <comment ref="G213" authorId="7" shapeId="0" xr:uid="{80809EA6-1C75-4782-B75F-9B8D8E1FF3DD}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -153,7 +162,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="I212" authorId="7" shapeId="0" xr:uid="{4AD49B9C-A1D0-4A25-B5DF-3F2CF529CCE3}">
+    <comment ref="I213" authorId="8" shapeId="0" xr:uid="{4AD49B9C-A1D0-4A25-B5DF-3F2CF529CCE3}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -162,7 +171,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="G213" authorId="8" shapeId="0" xr:uid="{C9E6BF89-D9D3-4E3C-B697-A5DC0E655E3C}">
+    <comment ref="G214" authorId="9" shapeId="0" xr:uid="{C9E6BF89-D9D3-4E3C-B697-A5DC0E655E3C}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -171,7 +180,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="I213" authorId="9" shapeId="0" xr:uid="{30CBB802-82F2-45BB-8B27-7315D97962A6}">
+    <comment ref="I214" authorId="10" shapeId="0" xr:uid="{30CBB802-82F2-45BB-8B27-7315D97962A6}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -180,7 +189,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="G214" authorId="10" shapeId="0" xr:uid="{1FC59F05-C26A-4351-8236-C828500ADDBC}">
+    <comment ref="G215" authorId="11" shapeId="0" xr:uid="{1FC59F05-C26A-4351-8236-C828500ADDBC}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -189,7 +198,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="I214" authorId="11" shapeId="0" xr:uid="{1348B42C-4137-429B-A693-D62CB5C3BC03}">
+    <comment ref="I215" authorId="12" shapeId="0" xr:uid="{1348B42C-4137-429B-A693-D62CB5C3BC03}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -198,7 +207,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="J256" authorId="1" shapeId="0" xr:uid="{F52DD24B-5ABC-4F49-A632-F9389FACE903}">
+    <comment ref="J257" authorId="1" shapeId="0" xr:uid="{F52DD24B-5ABC-4F49-A632-F9389FACE903}">
       <text>
         <r>
           <rPr>
@@ -227,7 +236,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="21">
   <si>
     <t>smolt_year</t>
   </si>
@@ -300,7 +309,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,6 +351,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -409,9 +424,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -449,7 +464,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -555,7 +570,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -697,7 +712,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -714,33 +729,36 @@
   <threadedComment ref="G113" dT="2025-03-04T16:50:12.85" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{C335BF2D-8A76-4A85-B639-EC939DD5E53A}">
     <text>1977-1985 average CV applied to guesstimated mean</text>
   </threadedComment>
-  <threadedComment ref="G211" dT="2025-07-23T21:51:33.73" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{288476D4-5EF1-4853-B334-5E56430540C8}">
+  <threadedComment ref="F211" dT="2026-03-31T23:00:59.33" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{3E6EE213-51C5-4BE7-94A1-C3C937E7343E}">
+    <text>Assuming 50/50 Sk/Stickle. Tows caught 3 Sk, 6 Stickle, but notes indicate they likely hit a pocket of stickles at a shallower depth</text>
+  </threadedComment>
+  <threadedComment ref="G212" dT="2025-07-23T21:51:33.73" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{288476D4-5EF1-4853-B334-5E56430540C8}">
     <text xml:space="preserve">Converts 95% CI of the total limnetic fish estimate to a coefficient of variation, and then multiplies that by the species specific estimate to yield and SD value. </text>
   </threadedComment>
-  <threadedComment ref="I211" dT="2025-07-23T21:51:33.73" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{FC5C3F1C-3F41-443B-A044-4AEECF017EAF}">
+  <threadedComment ref="I212" dT="2025-07-23T21:51:33.73" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{FC5C3F1C-3F41-443B-A044-4AEECF017EAF}">
     <text xml:space="preserve">Converts 95% CI of the total limnetic fish estimate to a coefficient of variation, and then multiplies that by the species specific estimate to yield and SD value. </text>
   </threadedComment>
-  <threadedComment ref="G212" dT="2025-07-23T21:53:41.91" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{80809EA6-1C75-4782-B75F-9B8D8E1FF3DD}">
+  <threadedComment ref="G213" dT="2025-07-23T21:53:41.91" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{80809EA6-1C75-4782-B75F-9B8D8E1FF3DD}">
     <text xml:space="preserve">Converts 95% CI of the total limnetic fish estimate to a coefficient of variation, and then multiplies that by the species specific estimate to yield and SD value. 
 </text>
   </threadedComment>
-  <threadedComment ref="I212" dT="2025-07-23T21:53:41.91" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{4AD49B9C-A1D0-4A25-B5DF-3F2CF529CCE3}">
+  <threadedComment ref="I213" dT="2025-07-23T21:53:41.91" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{4AD49B9C-A1D0-4A25-B5DF-3F2CF529CCE3}">
     <text xml:space="preserve">Converts 95% CI of the total limnetic fish estimate to a coefficient of variation, and then multiplies that by the species specific estimate to yield and SD value. 
 </text>
   </threadedComment>
-  <threadedComment ref="G213" dT="2025-07-23T21:53:45.87" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{C9E6BF89-D9D3-4E3C-B697-A5DC0E655E3C}">
+  <threadedComment ref="G214" dT="2025-07-23T21:53:45.87" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{C9E6BF89-D9D3-4E3C-B697-A5DC0E655E3C}">
     <text xml:space="preserve">Converts 95% CI of the total limnetic fish estimate to a coefficient of variation, and then multiplies that by the species specific estimate to yield and SD value. 
 </text>
   </threadedComment>
-  <threadedComment ref="I213" dT="2025-07-23T21:53:45.87" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{30CBB802-82F2-45BB-8B27-7315D97962A6}">
+  <threadedComment ref="I214" dT="2025-07-23T21:53:45.87" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{30CBB802-82F2-45BB-8B27-7315D97962A6}">
     <text xml:space="preserve">Converts 95% CI of the total limnetic fish estimate to a coefficient of variation, and then multiplies that by the species specific estimate to yield and SD value. 
 </text>
   </threadedComment>
-  <threadedComment ref="G214" dT="2025-07-23T21:53:49.52" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{1FC59F05-C26A-4351-8236-C828500ADDBC}">
+  <threadedComment ref="G215" dT="2025-07-23T21:53:49.52" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{1FC59F05-C26A-4351-8236-C828500ADDBC}">
     <text xml:space="preserve">Converts 95% CI of the total limnetic fish estimate to a coefficient of variation, and then multiplies that by the species specific estimate to yield and SD value. 
 </text>
   </threadedComment>
-  <threadedComment ref="I214" dT="2025-07-23T21:53:49.52" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{1348B42C-4137-429B-A693-D62CB5C3BC03}">
+  <threadedComment ref="I215" dT="2025-07-23T21:53:49.52" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{1348B42C-4137-429B-A693-D62CB5C3BC03}">
     <text xml:space="preserve">Converts 95% CI of the total limnetic fish estimate to a coefficient of variation, and then multiplies that by the species specific estimate to yield and SD value. 
 </text>
   </threadedComment>
@@ -749,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47CDFEE8-69FE-4C98-AD8C-E5081C486B0D}">
-  <dimension ref="A1:J313"/>
+  <dimension ref="A1:J314"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -7240,7 +7258,7 @@
         <v>13</v>
       </c>
       <c r="B197">
-        <f t="shared" ref="B197:B264" si="20">YEAR(C197)</f>
+        <f t="shared" ref="B197:B265" si="20">YEAR(C197)</f>
         <v>2009</v>
       </c>
       <c r="C197" s="2">
@@ -7461,11 +7479,11 @@
         <v>40973</v>
       </c>
       <c r="D203" s="4">
-        <f t="shared" ref="D203:D270" si="21">IF(MONTH(C203)&lt;4,B203-2,B203-1)</f>
+        <f t="shared" ref="D203:D271" si="21">IF(MONTH(C203)&lt;4,B203-2,B203-1)</f>
         <v>2010</v>
       </c>
       <c r="E203" s="4">
-        <f t="shared" ref="E203:E270" si="22">IF(MONTH(C203)&lt;4,B203-3,B203-2)</f>
+        <f t="shared" ref="E203:E271" si="22">IF(MONTH(C203)&lt;4,B203-3,B203-2)</f>
         <v>2009</v>
       </c>
       <c r="F203">
@@ -7736,33 +7754,34 @@
         <v>13</v>
       </c>
       <c r="B211">
-        <f>YEAR(C211)</f>
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C211" s="2">
-        <v>44167</v>
+        <v>43812</v>
       </c>
       <c r="D211" s="4">
-        <f>IF(MONTH(C211)&lt;4,B211-2,B211-1)</f>
-        <v>2019</v>
+        <f t="shared" si="21"/>
+        <v>2018</v>
       </c>
       <c r="E211" s="4">
-        <f>IF(MONTH(C211)&lt;4,B211-3,B211-2)</f>
-        <v>2018</v>
+        <f t="shared" si="22"/>
+        <v>2017</v>
       </c>
       <c r="F211">
-        <v>91633</v>
+        <f>943224/2</f>
+        <v>471612</v>
       </c>
       <c r="G211">
-        <f>(((1243193-976715)/1.96)/1104016)*F211</f>
-        <v>11284.487158238464</v>
+        <f>(((1046327-847837)/1.96)/943224)*F211</f>
+        <v>50635.204081632655</v>
       </c>
       <c r="H211">
-        <v>1012383</v>
+        <f>943224/2</f>
+        <v>471612</v>
       </c>
       <c r="I211">
-        <f>(((1243193-976715)/1.96)/1104016)*H211</f>
-        <v>124673.67610706766</v>
+        <f>(((1046327-847837)/1.96)/943224)*H211</f>
+        <v>50635.204081632655</v>
       </c>
       <c r="J211">
         <v>1</v>
@@ -7774,32 +7793,35 @@
       </c>
       <c r="B212">
         <f>YEAR(C212)</f>
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C212" s="2">
-        <v>44532</v>
+        <v>44167</v>
       </c>
       <c r="D212" s="4">
         <f>IF(MONTH(C212)&lt;4,B212-2,B212-1)</f>
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E212" s="4">
         <f>IF(MONTH(C212)&lt;4,B212-3,B212-2)</f>
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="F212">
-        <v>28482</v>
+        <v>91633</v>
       </c>
       <c r="G212">
-        <f>(((879230-775151)/1.96)/775151)*F212</f>
-        <v>1951.1524785467077</v>
+        <f>(((1243193-976715)/1.96)/1104016)*F212</f>
+        <v>11284.487158238464</v>
       </c>
       <c r="H212">
-        <v>797496</v>
+        <v>1012383</v>
       </c>
       <c r="I212">
-        <f>(((879230-775151)/1.96)/775151)*H212</f>
-        <v>54632.269399307814</v>
+        <f>(((1243193-976715)/1.96)/1104016)*H212</f>
+        <v>124673.67610706766</v>
+      </c>
+      <c r="J212">
+        <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
@@ -7808,10 +7830,10 @@
       </c>
       <c r="B213">
         <f>YEAR(C213)</f>
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C213" s="2">
-        <v>44615</v>
+        <v>44532</v>
       </c>
       <c r="D213" s="4">
         <f>IF(MONTH(C213)&lt;4,B213-2,B213-1)</f>
@@ -7822,21 +7844,18 @@
         <v>2019</v>
       </c>
       <c r="F213">
-        <v>17933</v>
+        <v>28482</v>
       </c>
       <c r="G213">
-        <f>(((706813-620703)/1.96)/662703)*F213</f>
-        <v>1188.8622298775329</v>
+        <f>(((879230-775151)/1.96)/775151)*F213</f>
+        <v>1951.1524785467077</v>
       </c>
       <c r="H213">
-        <v>644791</v>
+        <v>797496</v>
       </c>
       <c r="I213">
-        <f>(((706813-620703)/1.96)/662703)*H213</f>
-        <v>42746.203427478074</v>
-      </c>
-      <c r="J213">
-        <v>1</v>
+        <f>(((879230-775151)/1.96)/775151)*H213</f>
+        <v>54632.269399307814</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
@@ -7848,29 +7867,29 @@
         <v>2022</v>
       </c>
       <c r="C214" s="2">
-        <v>44883</v>
+        <v>44615</v>
       </c>
       <c r="D214" s="4">
         <f>IF(MONTH(C214)&lt;4,B214-2,B214-1)</f>
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E214" s="4">
         <f>IF(MONTH(C214)&lt;4,B214-3,B214-2)</f>
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="F214">
-        <v>1097034</v>
+        <v>17933</v>
       </c>
       <c r="G214">
-        <f>(((1818086-1300757)/1.96)/1706864)*F214</f>
-        <v>169641.42899146132</v>
+        <f>(((706813-620703)/1.96)/662703)*F214</f>
+        <v>1188.8622298775329</v>
       </c>
       <c r="H214">
-        <v>609830</v>
+        <v>644791</v>
       </c>
       <c r="I214">
-        <f>(((1818086-1300757)/1.96)/1706864)*H214</f>
-        <v>94301.938355477454</v>
+        <f>(((706813-620703)/1.96)/662703)*H214</f>
+        <v>42746.203427478074</v>
       </c>
       <c r="J214">
         <v>1</v>
@@ -7878,34 +7897,36 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B215">
-        <f t="shared" si="20"/>
-        <v>1980</v>
+        <f>YEAR(C215)</f>
+        <v>2022</v>
       </c>
       <c r="C215" s="2">
-        <v>29277</v>
+        <v>44883</v>
       </c>
       <c r="D215" s="4">
-        <f t="shared" si="21"/>
-        <v>1978</v>
+        <f>IF(MONTH(C215)&lt;4,B215-2,B215-1)</f>
+        <v>2021</v>
       </c>
       <c r="E215" s="4">
-        <f t="shared" si="22"/>
-        <v>1977</v>
+        <f>IF(MONTH(C215)&lt;4,B215-3,B215-2)</f>
+        <v>2020</v>
       </c>
       <c r="F215">
-        <v>4623613</v>
+        <v>1097034</v>
       </c>
       <c r="G215">
-        <v>698082</v>
+        <f>(((1818086-1300757)/1.96)/1706864)*F215</f>
+        <v>169641.42899146132</v>
       </c>
       <c r="H215">
-        <v>0</v>
+        <v>609830</v>
       </c>
       <c r="I215">
-        <v>0</v>
+        <f>(((1818086-1300757)/1.96)/1706864)*H215</f>
+        <v>94301.938355477454</v>
       </c>
       <c r="J215">
         <v>1</v>
@@ -7917,30 +7938,30 @@
       </c>
       <c r="B216">
         <f t="shared" si="20"/>
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="C216" s="2">
-        <v>29606</v>
+        <v>29277</v>
       </c>
       <c r="D216" s="4">
         <f t="shared" si="21"/>
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="E216" s="4">
         <f t="shared" si="22"/>
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="F216">
-        <v>5684292</v>
+        <v>4623613</v>
       </c>
       <c r="G216">
-        <v>1116531</v>
+        <v>698082</v>
       </c>
       <c r="H216">
-        <v>158639</v>
+        <v>0</v>
       </c>
       <c r="I216">
-        <v>163338</v>
+        <v>0</v>
       </c>
       <c r="J216">
         <v>1</v>
@@ -7955,27 +7976,30 @@
         <v>1981</v>
       </c>
       <c r="C217" s="2">
-        <v>29803</v>
+        <v>29606</v>
       </c>
       <c r="D217" s="4">
         <f t="shared" si="21"/>
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="E217" s="4">
         <f t="shared" si="22"/>
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="F217">
-        <v>14396081</v>
+        <v>5684292</v>
       </c>
       <c r="G217">
-        <v>3293857</v>
+        <v>1116531</v>
       </c>
       <c r="H217">
-        <v>123261</v>
+        <v>158639</v>
       </c>
       <c r="I217">
-        <v>36969</v>
+        <v>163338</v>
+      </c>
+      <c r="J217">
+        <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
@@ -7987,7 +8011,7 @@
         <v>1981</v>
       </c>
       <c r="C218" s="2">
-        <v>29858</v>
+        <v>29803</v>
       </c>
       <c r="D218" s="4">
         <f t="shared" si="21"/>
@@ -7998,16 +8022,16 @@
         <v>1979</v>
       </c>
       <c r="F218">
-        <v>11189652</v>
+        <v>14396081</v>
       </c>
       <c r="G218">
-        <v>1612712</v>
+        <v>3293857</v>
       </c>
       <c r="H218">
-        <v>0</v>
+        <v>123261</v>
       </c>
       <c r="I218">
-        <v>0</v>
+        <v>36969</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
@@ -8019,7 +8043,7 @@
         <v>1981</v>
       </c>
       <c r="C219" s="2">
-        <v>29923</v>
+        <v>29858</v>
       </c>
       <c r="D219" s="4">
         <f t="shared" si="21"/>
@@ -8030,19 +8054,16 @@
         <v>1979</v>
       </c>
       <c r="F219">
-        <v>8335707</v>
+        <v>11189652</v>
       </c>
       <c r="G219">
-        <v>1379346</v>
+        <v>1612712</v>
       </c>
       <c r="H219">
         <v>0</v>
       </c>
       <c r="I219">
         <v>0</v>
-      </c>
-      <c r="J219">
-        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
@@ -8051,30 +8072,33 @@
       </c>
       <c r="B220">
         <f t="shared" si="20"/>
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="C220" s="2">
-        <v>30188</v>
+        <v>29923</v>
       </c>
       <c r="D220" s="4">
         <f t="shared" si="21"/>
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="E220" s="4">
         <f t="shared" si="22"/>
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="F220">
-        <v>19786826</v>
+        <v>8335707</v>
       </c>
       <c r="G220">
-        <v>3687338</v>
+        <v>1379346</v>
       </c>
       <c r="H220">
-        <v>1171047</v>
+        <v>0</v>
       </c>
       <c r="I220">
-        <v>212426</v>
+        <v>0</v>
+      </c>
+      <c r="J220">
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
@@ -8086,7 +8110,7 @@
         <v>1982</v>
       </c>
       <c r="C221" s="2">
-        <v>30265</v>
+        <v>30188</v>
       </c>
       <c r="D221" s="4">
         <f t="shared" si="21"/>
@@ -8097,16 +8121,16 @@
         <v>1980</v>
       </c>
       <c r="F221">
-        <v>7249794</v>
+        <v>19786826</v>
       </c>
       <c r="G221">
-        <v>1890346</v>
+        <v>3687338</v>
       </c>
       <c r="H221">
-        <v>435913</v>
+        <v>1171047</v>
       </c>
       <c r="I221">
-        <v>137604</v>
+        <v>212426</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
@@ -8115,10 +8139,10 @@
       </c>
       <c r="B222">
         <f t="shared" si="20"/>
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="C222" s="2">
-        <v>30377</v>
+        <v>30265</v>
       </c>
       <c r="D222" s="4">
         <f t="shared" si="21"/>
@@ -8129,19 +8153,16 @@
         <v>1980</v>
       </c>
       <c r="F222">
-        <v>8427632</v>
+        <v>7249794</v>
       </c>
       <c r="G222">
-        <v>1378401</v>
+        <v>1890346</v>
       </c>
       <c r="H222">
-        <v>0</v>
+        <v>435913</v>
       </c>
       <c r="I222">
-        <v>0</v>
-      </c>
-      <c r="J222">
-        <v>1</v>
+        <v>137604</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
@@ -8153,27 +8174,30 @@
         <v>1983</v>
       </c>
       <c r="C223" s="2">
-        <v>30551</v>
+        <v>30377</v>
       </c>
       <c r="D223" s="4">
         <f t="shared" si="21"/>
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="E223" s="4">
         <f t="shared" si="22"/>
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="F223">
-        <v>13176917</v>
+        <v>8427632</v>
       </c>
       <c r="G223">
-        <v>4038902</v>
+        <v>1378401</v>
       </c>
       <c r="H223">
-        <v>4662</v>
+        <v>0</v>
       </c>
       <c r="I223">
-        <v>5826</v>
+        <v>0</v>
+      </c>
+      <c r="J223">
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
@@ -8185,7 +8209,7 @@
         <v>1983</v>
       </c>
       <c r="C224" s="2">
-        <v>30648</v>
+        <v>30551</v>
       </c>
       <c r="D224" s="4">
         <f t="shared" si="21"/>
@@ -8196,19 +8220,16 @@
         <v>1981</v>
       </c>
       <c r="F224">
-        <v>9639172</v>
+        <v>13176917</v>
       </c>
       <c r="G224">
-        <v>1563720</v>
+        <v>4038902</v>
       </c>
       <c r="H224">
-        <v>0</v>
+        <v>4662</v>
       </c>
       <c r="I224">
-        <v>0</v>
-      </c>
-      <c r="J224">
-        <v>1</v>
+        <v>5826</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
@@ -8217,24 +8238,24 @@
       </c>
       <c r="B225">
         <f t="shared" si="20"/>
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="C225" s="2">
-        <v>30956</v>
+        <v>30648</v>
       </c>
       <c r="D225" s="4">
         <f t="shared" si="21"/>
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E225" s="4">
         <f t="shared" si="22"/>
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="F225">
-        <v>19564054</v>
+        <v>9639172</v>
       </c>
       <c r="G225">
-        <v>3521352</v>
+        <v>1563720</v>
       </c>
       <c r="H225">
         <v>0</v>
@@ -8252,24 +8273,24 @@
       </c>
       <c r="B226">
         <f t="shared" si="20"/>
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="C226" s="2">
-        <v>31316</v>
+        <v>30956</v>
       </c>
       <c r="D226" s="4">
         <f t="shared" si="21"/>
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="E226" s="4">
         <f t="shared" si="22"/>
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="F226">
-        <v>6970095</v>
+        <v>19564054</v>
       </c>
       <c r="G226">
-        <v>1145018</v>
+        <v>3521352</v>
       </c>
       <c r="H226">
         <v>0</v>
@@ -8290,7 +8311,7 @@
         <v>1985</v>
       </c>
       <c r="C227" s="2">
-        <v>31317</v>
+        <v>31316</v>
       </c>
       <c r="D227" s="4">
         <f t="shared" si="21"/>
@@ -8301,16 +8322,19 @@
         <v>1983</v>
       </c>
       <c r="F227">
-        <v>9079741</v>
+        <v>6970095</v>
       </c>
       <c r="G227">
-        <v>1433266</v>
+        <v>1145018</v>
       </c>
       <c r="H227">
         <v>0</v>
       </c>
       <c r="I227">
         <v>0</v>
+      </c>
+      <c r="J227">
+        <v>1</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
@@ -8319,24 +8343,24 @@
       </c>
       <c r="B228">
         <f t="shared" si="20"/>
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="C228" s="2">
-        <v>31651</v>
+        <v>31317</v>
       </c>
       <c r="D228" s="4">
         <f t="shared" si="21"/>
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="E228" s="4">
         <f t="shared" si="22"/>
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="F228">
-        <v>8825549</v>
+        <v>9079741</v>
       </c>
       <c r="G228">
-        <v>2013110</v>
+        <v>1433266</v>
       </c>
       <c r="H228">
         <v>0</v>
@@ -8354,7 +8378,7 @@
         <v>1986</v>
       </c>
       <c r="C229" s="2">
-        <v>31652</v>
+        <v>31651</v>
       </c>
       <c r="D229" s="4">
         <f t="shared" si="21"/>
@@ -8365,10 +8389,10 @@
         <v>1984</v>
       </c>
       <c r="F229">
-        <v>11232287</v>
+        <v>8825549</v>
       </c>
       <c r="G229">
-        <v>2012645</v>
+        <v>2013110</v>
       </c>
       <c r="H229">
         <v>0</v>
@@ -8386,7 +8410,7 @@
         <v>1986</v>
       </c>
       <c r="C230" s="2">
-        <v>31715</v>
+        <v>31652</v>
       </c>
       <c r="D230" s="4">
         <f t="shared" si="21"/>
@@ -8397,19 +8421,16 @@
         <v>1984</v>
       </c>
       <c r="F230">
-        <v>4983068</v>
+        <v>11232287</v>
       </c>
       <c r="G230">
-        <v>114988</v>
+        <v>2012645</v>
       </c>
       <c r="H230">
-        <v>53880</v>
+        <v>0</v>
       </c>
       <c r="I230">
-        <v>23107</v>
-      </c>
-      <c r="J230">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
@@ -8418,10 +8439,10 @@
       </c>
       <c r="B231">
         <f t="shared" si="20"/>
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="C231" s="2">
-        <v>31831</v>
+        <v>31715</v>
       </c>
       <c r="D231" s="4">
         <f t="shared" si="21"/>
@@ -8432,16 +8453,19 @@
         <v>1984</v>
       </c>
       <c r="F231">
-        <v>4762461</v>
+        <v>4983068</v>
       </c>
       <c r="G231">
-        <v>785400</v>
+        <v>114988</v>
       </c>
       <c r="H231">
-        <v>98338</v>
+        <v>53880</v>
       </c>
       <c r="I231">
-        <v>78489</v>
+        <v>23107</v>
+      </c>
+      <c r="J231">
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
@@ -8453,27 +8477,27 @@
         <v>1987</v>
       </c>
       <c r="C232" s="2">
-        <v>32021</v>
+        <v>31831</v>
       </c>
       <c r="D232" s="4">
         <f t="shared" si="21"/>
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="E232" s="4">
         <f t="shared" si="22"/>
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="F232">
-        <v>8560289</v>
+        <v>4762461</v>
       </c>
       <c r="G232">
-        <v>1390335</v>
+        <v>785400</v>
       </c>
       <c r="H232">
-        <v>57659</v>
+        <v>98338</v>
       </c>
       <c r="I232">
-        <v>14564</v>
+        <v>78489</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
@@ -8485,7 +8509,7 @@
         <v>1987</v>
       </c>
       <c r="C233" s="2">
-        <v>32119</v>
+        <v>32021</v>
       </c>
       <c r="D233" s="4">
         <f t="shared" si="21"/>
@@ -8496,16 +8520,16 @@
         <v>1985</v>
       </c>
       <c r="F233">
-        <v>10840544</v>
+        <v>8560289</v>
       </c>
       <c r="G233">
-        <v>1397888</v>
+        <v>1390335</v>
       </c>
       <c r="H233">
-        <v>200451</v>
+        <v>57659</v>
       </c>
       <c r="I233">
-        <v>41137</v>
+        <v>14564</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
@@ -8514,10 +8538,10 @@
       </c>
       <c r="B234">
         <f t="shared" si="20"/>
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="C234" s="2">
-        <v>32169</v>
+        <v>32119</v>
       </c>
       <c r="D234" s="4">
         <f t="shared" si="21"/>
@@ -8528,19 +8552,16 @@
         <v>1985</v>
       </c>
       <c r="F234">
-        <v>8892056</v>
+        <v>10840544</v>
       </c>
       <c r="G234">
-        <v>950613</v>
+        <v>1397888</v>
       </c>
       <c r="H234">
-        <v>0</v>
+        <v>200451</v>
       </c>
       <c r="I234">
-        <v>0</v>
-      </c>
-      <c r="J234">
-        <v>1</v>
+        <v>41137</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
@@ -8552,21 +8573,21 @@
         <v>1988</v>
       </c>
       <c r="C235" s="2">
-        <v>32448</v>
+        <v>32169</v>
       </c>
       <c r="D235" s="4">
         <f t="shared" si="21"/>
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="E235" s="4">
         <f t="shared" si="22"/>
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="F235">
-        <v>9187558</v>
+        <v>8892056</v>
       </c>
       <c r="G235">
-        <v>1141438</v>
+        <v>950613</v>
       </c>
       <c r="H235">
         <v>0</v>
@@ -8584,30 +8605,33 @@
       </c>
       <c r="B236">
         <f t="shared" si="20"/>
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="C236" s="2">
-        <v>32687</v>
+        <v>32448</v>
       </c>
       <c r="D236" s="4">
         <f t="shared" si="21"/>
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="E236" s="4">
         <f t="shared" si="22"/>
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="F236">
-        <v>11813897</v>
+        <v>9187558</v>
       </c>
       <c r="G236">
-        <v>1910313</v>
+        <v>1141438</v>
       </c>
       <c r="H236">
-        <v>1923193</v>
+        <v>0</v>
       </c>
       <c r="I236">
-        <v>310981</v>
+        <v>0</v>
+      </c>
+      <c r="J236">
+        <v>1</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
@@ -8619,7 +8643,7 @@
         <v>1989</v>
       </c>
       <c r="C237" s="2">
-        <v>32799</v>
+        <v>32687</v>
       </c>
       <c r="D237" s="4">
         <f t="shared" si="21"/>
@@ -8630,19 +8654,16 @@
         <v>1987</v>
       </c>
       <c r="F237">
-        <v>11183261</v>
+        <v>11813897</v>
       </c>
       <c r="G237">
-        <v>1959673</v>
+        <v>1910313</v>
       </c>
       <c r="H237">
-        <v>0</v>
+        <v>1923193</v>
       </c>
       <c r="I237">
-        <v>0</v>
-      </c>
-      <c r="J237">
-        <v>1</v>
+        <v>310981</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
@@ -8654,7 +8675,7 @@
         <v>1989</v>
       </c>
       <c r="C238" s="2">
-        <v>32800</v>
+        <v>32799</v>
       </c>
       <c r="D238" s="4">
         <f t="shared" si="21"/>
@@ -8665,16 +8686,19 @@
         <v>1987</v>
       </c>
       <c r="F238">
-        <v>13224299</v>
+        <v>11183261</v>
       </c>
       <c r="G238">
-        <v>2304833</v>
+        <v>1959673</v>
       </c>
       <c r="H238">
-        <v>42305</v>
+        <v>0</v>
       </c>
       <c r="I238">
-        <v>11020</v>
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
@@ -8683,10 +8707,10 @@
       </c>
       <c r="B239">
         <f t="shared" si="20"/>
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="C239" s="2">
-        <v>32946</v>
+        <v>32800</v>
       </c>
       <c r="D239" s="4">
         <f t="shared" si="21"/>
@@ -8697,16 +8721,16 @@
         <v>1987</v>
       </c>
       <c r="F239">
-        <v>7487085</v>
+        <v>13224299</v>
       </c>
       <c r="G239">
-        <v>1092031</v>
+        <v>2304833</v>
       </c>
       <c r="H239">
-        <v>0</v>
+        <v>42305</v>
       </c>
       <c r="I239">
-        <v>0</v>
+        <v>11020</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
@@ -8718,27 +8742,27 @@
         <v>1990</v>
       </c>
       <c r="C240" s="2">
-        <v>33035</v>
+        <v>32946</v>
       </c>
       <c r="D240" s="4">
         <f t="shared" si="21"/>
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="E240" s="4">
         <f t="shared" si="22"/>
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="F240">
-        <v>4226888</v>
+        <v>7487085</v>
       </c>
       <c r="G240">
-        <v>965642</v>
+        <v>1092031</v>
       </c>
       <c r="H240">
-        <v>1286444</v>
+        <v>0</v>
       </c>
       <c r="I240">
-        <v>293891</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
@@ -8750,7 +8774,7 @@
         <v>1990</v>
       </c>
       <c r="C241" s="2">
-        <v>33036</v>
+        <v>33035</v>
       </c>
       <c r="D241" s="4">
         <f t="shared" si="21"/>
@@ -8761,16 +8785,16 @@
         <v>1988</v>
       </c>
       <c r="F241">
-        <v>4876891</v>
+        <v>4226888</v>
       </c>
       <c r="G241">
-        <v>1186063</v>
+        <v>965642</v>
       </c>
       <c r="H241">
-        <v>1484271</v>
+        <v>1286444</v>
       </c>
       <c r="I241">
-        <v>360976</v>
+        <v>293891</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
@@ -8782,7 +8806,7 @@
         <v>1990</v>
       </c>
       <c r="C242" s="2">
-        <v>33037</v>
+        <v>33036</v>
       </c>
       <c r="D242" s="4">
         <f t="shared" si="21"/>
@@ -8793,16 +8817,16 @@
         <v>1988</v>
       </c>
       <c r="F242">
-        <v>5477969</v>
+        <v>4876891</v>
       </c>
       <c r="G242">
-        <v>1287579</v>
+        <v>1186063</v>
       </c>
       <c r="H242">
-        <v>1667208</v>
+        <v>1484271</v>
       </c>
       <c r="I242">
-        <v>391872</v>
+        <v>360976</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
@@ -8814,7 +8838,7 @@
         <v>1990</v>
       </c>
       <c r="C243" s="2">
-        <v>33161</v>
+        <v>33037</v>
       </c>
       <c r="D243" s="4">
         <f t="shared" si="21"/>
@@ -8825,16 +8849,16 @@
         <v>1988</v>
       </c>
       <c r="F243">
-        <v>10173989</v>
+        <v>5477969</v>
       </c>
       <c r="G243">
-        <v>2119602</v>
+        <v>1287579</v>
       </c>
       <c r="H243">
-        <v>2594501</v>
+        <v>1667208</v>
       </c>
       <c r="I243">
-        <v>659443</v>
+        <v>391872</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
@@ -8846,7 +8870,7 @@
         <v>1990</v>
       </c>
       <c r="C244" s="2">
-        <v>33162</v>
+        <v>33161</v>
       </c>
       <c r="D244" s="4">
         <f t="shared" si="21"/>
@@ -8857,16 +8881,16 @@
         <v>1988</v>
       </c>
       <c r="F244">
-        <v>9156313</v>
+        <v>10173989</v>
       </c>
       <c r="G244">
-        <v>1485174</v>
+        <v>2119602</v>
       </c>
       <c r="H244">
-        <v>2250977</v>
+        <v>2594501</v>
       </c>
       <c r="I244">
-        <v>360135</v>
+        <v>659443</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
@@ -8878,7 +8902,7 @@
         <v>1990</v>
       </c>
       <c r="C245" s="2">
-        <v>33163</v>
+        <v>33162</v>
       </c>
       <c r="D245" s="4">
         <f t="shared" si="21"/>
@@ -8889,16 +8913,16 @@
         <v>1988</v>
       </c>
       <c r="F245">
-        <v>10967889</v>
+        <v>9156313</v>
       </c>
       <c r="G245">
-        <v>1980273</v>
+        <v>1485174</v>
       </c>
       <c r="H245">
-        <v>2706287</v>
+        <v>2250977</v>
       </c>
       <c r="I245">
-        <v>607388</v>
+        <v>360135</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
@@ -8910,7 +8934,7 @@
         <v>1990</v>
       </c>
       <c r="C246" s="2">
-        <v>33164</v>
+        <v>33163</v>
       </c>
       <c r="D246" s="4">
         <f t="shared" si="21"/>
@@ -8921,16 +8945,16 @@
         <v>1988</v>
       </c>
       <c r="F246">
-        <v>9142123</v>
+        <v>10967889</v>
       </c>
       <c r="G246">
-        <v>1627897</v>
+        <v>1980273</v>
       </c>
       <c r="H246">
-        <v>2244214</v>
+        <v>2706287</v>
       </c>
       <c r="I246">
-        <v>445150</v>
+        <v>607388</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
@@ -8939,10 +8963,10 @@
       </c>
       <c r="B247">
         <f t="shared" si="20"/>
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="C247" s="2">
-        <v>33275</v>
+        <v>33164</v>
       </c>
       <c r="D247" s="4">
         <f t="shared" si="21"/>
@@ -8953,19 +8977,16 @@
         <v>1988</v>
       </c>
       <c r="F247">
-        <v>8541187</v>
+        <v>9142123</v>
       </c>
       <c r="G247">
-        <v>1149338</v>
+        <v>1627897</v>
       </c>
       <c r="H247">
-        <v>0</v>
+        <v>2244214</v>
       </c>
       <c r="I247">
-        <v>0</v>
-      </c>
-      <c r="J247">
-        <v>1</v>
+        <v>445150</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
@@ -8977,7 +8998,7 @@
         <v>1991</v>
       </c>
       <c r="C248" s="2">
-        <v>33278</v>
+        <v>33275</v>
       </c>
       <c r="D248" s="4">
         <f t="shared" si="21"/>
@@ -8988,16 +9009,19 @@
         <v>1988</v>
       </c>
       <c r="F248">
-        <v>8659533</v>
+        <v>8541187</v>
       </c>
       <c r="G248">
-        <v>2139007</v>
+        <v>1149338</v>
       </c>
       <c r="H248">
         <v>0</v>
       </c>
       <c r="I248">
         <v>0</v>
+      </c>
+      <c r="J248">
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
@@ -9009,21 +9033,21 @@
         <v>1991</v>
       </c>
       <c r="C249" s="2">
-        <v>33438</v>
+        <v>33278</v>
       </c>
       <c r="D249" s="4">
         <f t="shared" si="21"/>
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="E249" s="4">
         <f t="shared" si="22"/>
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="F249">
-        <v>5960245</v>
+        <v>8659533</v>
       </c>
       <c r="G249">
-        <v>1254240</v>
+        <v>2139007</v>
       </c>
       <c r="H249">
         <v>0</v>
@@ -9041,7 +9065,7 @@
         <v>1991</v>
       </c>
       <c r="C250" s="2">
-        <v>33527</v>
+        <v>33438</v>
       </c>
       <c r="D250" s="4">
         <f t="shared" si="21"/>
@@ -9052,19 +9076,16 @@
         <v>1989</v>
       </c>
       <c r="F250">
-        <v>5883006</v>
+        <v>5960245</v>
       </c>
       <c r="G250">
-        <v>1124826</v>
+        <v>1254240</v>
       </c>
       <c r="H250">
         <v>0</v>
       </c>
       <c r="I250">
         <v>0</v>
-      </c>
-      <c r="J250">
-        <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
@@ -9073,10 +9094,10 @@
       </c>
       <c r="B251">
         <f t="shared" si="20"/>
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="C251" s="2">
-        <v>33658</v>
+        <v>33527</v>
       </c>
       <c r="D251" s="4">
         <f t="shared" si="21"/>
@@ -9087,16 +9108,19 @@
         <v>1989</v>
       </c>
       <c r="F251">
-        <v>4776046</v>
+        <v>5883006</v>
       </c>
       <c r="G251">
-        <v>731461</v>
+        <v>1124826</v>
       </c>
       <c r="H251">
-        <v>162138</v>
+        <v>0</v>
       </c>
       <c r="I251">
-        <v>252918</v>
+        <v>0</v>
+      </c>
+      <c r="J251">
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
@@ -9108,27 +9132,27 @@
         <v>1992</v>
       </c>
       <c r="C252" s="2">
-        <v>33798</v>
+        <v>33658</v>
       </c>
       <c r="D252" s="4">
         <f t="shared" si="21"/>
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="E252" s="4">
         <f t="shared" si="22"/>
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="F252">
-        <v>6032231</v>
+        <v>4776046</v>
       </c>
       <c r="G252">
-        <v>1248407</v>
+        <v>731461</v>
       </c>
       <c r="H252">
-        <v>0</v>
+        <v>162138</v>
       </c>
       <c r="I252">
-        <v>0</v>
+        <v>252918</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
@@ -9140,7 +9164,7 @@
         <v>1992</v>
       </c>
       <c r="C253" s="2">
-        <v>33903</v>
+        <v>33798</v>
       </c>
       <c r="D253" s="4">
         <f t="shared" si="21"/>
@@ -9151,19 +9175,16 @@
         <v>1990</v>
       </c>
       <c r="F253">
-        <v>3372678</v>
+        <v>6032231</v>
       </c>
       <c r="G253">
-        <v>692662</v>
+        <v>1248407</v>
       </c>
       <c r="H253">
         <v>0</v>
       </c>
       <c r="I253">
         <v>0</v>
-      </c>
-      <c r="J253">
-        <v>1</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
@@ -9172,10 +9193,10 @@
       </c>
       <c r="B254">
         <f t="shared" si="20"/>
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="C254" s="2">
-        <v>34010</v>
+        <v>33903</v>
       </c>
       <c r="D254" s="4">
         <f t="shared" si="21"/>
@@ -9186,16 +9207,19 @@
         <v>1990</v>
       </c>
       <c r="F254">
-        <v>4560412</v>
+        <v>3372678</v>
       </c>
       <c r="G254">
-        <v>604464</v>
+        <v>692662</v>
       </c>
       <c r="H254">
         <v>0</v>
       </c>
       <c r="I254">
         <v>0</v>
+      </c>
+      <c r="J254">
+        <v>1</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
@@ -9207,21 +9231,21 @@
         <v>1993</v>
       </c>
       <c r="C255" s="2">
-        <v>34177</v>
+        <v>34010</v>
       </c>
       <c r="D255" s="4">
         <f t="shared" si="21"/>
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="E255" s="4">
         <f t="shared" si="22"/>
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="F255">
-        <v>10198355</v>
+        <v>4560412</v>
       </c>
       <c r="G255">
-        <v>3860607</v>
+        <v>604464</v>
       </c>
       <c r="H255">
         <v>0</v>
@@ -9239,7 +9263,7 @@
         <v>1993</v>
       </c>
       <c r="C256" s="2">
-        <v>34254</v>
+        <v>34177</v>
       </c>
       <c r="D256" s="4">
         <f t="shared" si="21"/>
@@ -9250,19 +9274,16 @@
         <v>1991</v>
       </c>
       <c r="F256">
-        <v>5992046</v>
+        <v>10198355</v>
       </c>
       <c r="G256">
-        <v>806992</v>
+        <v>3860607</v>
       </c>
       <c r="H256">
-        <v>57164</v>
+        <v>0</v>
       </c>
       <c r="I256">
-        <v>58691</v>
-      </c>
-      <c r="J256">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
@@ -9271,10 +9292,10 @@
       </c>
       <c r="B257">
         <f t="shared" si="20"/>
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="C257" s="2">
-        <v>34365</v>
+        <v>34254</v>
       </c>
       <c r="D257" s="4">
         <f t="shared" si="21"/>
@@ -9285,16 +9306,19 @@
         <v>1991</v>
       </c>
       <c r="F257">
-        <v>5895395</v>
+        <v>5992046</v>
       </c>
       <c r="G257">
-        <v>780598</v>
+        <v>806992</v>
       </c>
       <c r="H257">
-        <v>0</v>
+        <v>57164</v>
       </c>
       <c r="I257">
-        <v>0</v>
+        <v>58691</v>
+      </c>
+      <c r="J257">
+        <v>1</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
@@ -9306,27 +9330,27 @@
         <v>1994</v>
       </c>
       <c r="C258" s="2">
-        <v>34626</v>
+        <v>34365</v>
       </c>
       <c r="D258" s="4">
         <f t="shared" si="21"/>
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="E258" s="4">
         <f t="shared" si="22"/>
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="F258">
-        <v>6769766</v>
+        <v>5895395</v>
       </c>
       <c r="G258">
-        <v>732204</v>
+        <v>780598</v>
       </c>
       <c r="H258">
-        <v>109137</v>
+        <v>0</v>
       </c>
       <c r="I258">
-        <v>23773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.25">
@@ -9335,34 +9359,30 @@
       </c>
       <c r="B259">
         <f t="shared" si="20"/>
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="C259" s="2">
-        <v>34730</v>
+        <v>34626</v>
       </c>
       <c r="D259" s="4">
-        <f t="shared" ref="D259" si="23">IF(MONTH(C259)&lt;4,B259-2,B259-1)</f>
+        <f t="shared" si="21"/>
         <v>1993</v>
       </c>
       <c r="E259" s="4">
-        <f t="shared" ref="E259" si="24">IF(MONTH(C259)&lt;4,B259-3,B259-2)</f>
+        <f t="shared" si="22"/>
         <v>1992</v>
       </c>
       <c r="F259">
-        <v>5895000</v>
+        <v>6769766</v>
       </c>
       <c r="G259">
-        <f>0.13*F259</f>
-        <v>766350</v>
+        <v>732204</v>
       </c>
       <c r="H259">
-        <v>0</v>
+        <v>109137</v>
       </c>
       <c r="I259">
-        <v>0</v>
-      </c>
-      <c r="J259">
-        <v>1</v>
+        <v>23773</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
@@ -9374,27 +9394,31 @@
         <v>1995</v>
       </c>
       <c r="C260" s="2">
-        <v>34894</v>
+        <v>34730</v>
       </c>
       <c r="D260" s="4">
-        <f t="shared" si="21"/>
-        <v>1994</v>
+        <f t="shared" ref="D260" si="23">IF(MONTH(C260)&lt;4,B260-2,B260-1)</f>
+        <v>1993</v>
       </c>
       <c r="E260" s="4">
-        <f t="shared" si="22"/>
-        <v>1993</v>
+        <f t="shared" ref="E260" si="24">IF(MONTH(C260)&lt;4,B260-3,B260-2)</f>
+        <v>1992</v>
       </c>
       <c r="F260">
-        <v>10913020</v>
+        <v>5895000</v>
       </c>
       <c r="G260">
-        <v>1990404</v>
+        <f>0.13*F260</f>
+        <v>766350</v>
       </c>
       <c r="H260">
         <v>0</v>
       </c>
       <c r="I260">
         <v>0</v>
+      </c>
+      <c r="J260">
+        <v>1</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.25">
@@ -9406,7 +9430,7 @@
         <v>1995</v>
       </c>
       <c r="C261" s="2">
-        <v>35023</v>
+        <v>34894</v>
       </c>
       <c r="D261" s="4">
         <f t="shared" si="21"/>
@@ -9417,16 +9441,16 @@
         <v>1993</v>
       </c>
       <c r="F261">
-        <v>10634355</v>
+        <v>10913020</v>
       </c>
       <c r="G261">
-        <v>1445908</v>
+        <v>1990404</v>
       </c>
       <c r="H261">
-        <v>3462461</v>
+        <v>0</v>
       </c>
       <c r="I261">
-        <v>545953</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.25">
@@ -9438,7 +9462,7 @@
         <v>1995</v>
       </c>
       <c r="C262" s="2">
-        <v>35024</v>
+        <v>35023</v>
       </c>
       <c r="D262" s="4">
         <f t="shared" si="21"/>
@@ -9449,16 +9473,16 @@
         <v>1993</v>
       </c>
       <c r="F262">
-        <v>11699308</v>
+        <v>10634355</v>
       </c>
       <c r="G262">
-        <v>1924264</v>
+        <v>1445908</v>
       </c>
       <c r="H262">
-        <v>2394737</v>
+        <v>3462461</v>
       </c>
       <c r="I262">
-        <v>962122</v>
+        <v>545953</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.25">
@@ -9467,10 +9491,10 @@
       </c>
       <c r="B263">
         <f t="shared" si="20"/>
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="C263" s="2">
-        <v>35094</v>
+        <v>35024</v>
       </c>
       <c r="D263" s="4">
         <f t="shared" si="21"/>
@@ -9481,21 +9505,16 @@
         <v>1993</v>
       </c>
       <c r="F263">
-        <v>6152000</v>
-      </c>
-      <c r="G263" s="9">
-        <f>0.13*F263</f>
-        <v>799760</v>
+        <v>11699308</v>
+      </c>
+      <c r="G263">
+        <v>1924264</v>
       </c>
       <c r="H263">
-        <v>346000</v>
+        <v>2394737</v>
       </c>
       <c r="I263">
-        <f>0.13*H263</f>
-        <v>44980</v>
-      </c>
-      <c r="J263">
-        <v>1</v>
+        <v>962122</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.25">
@@ -9507,27 +9526,32 @@
         <v>1996</v>
       </c>
       <c r="C264" s="2">
-        <v>35268</v>
+        <v>35094</v>
       </c>
       <c r="D264" s="4">
         <f t="shared" si="21"/>
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="E264" s="4">
         <f t="shared" si="22"/>
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="F264">
-        <v>7258271</v>
+        <v>6152000</v>
       </c>
       <c r="G264" s="9">
-        <v>1351084</v>
+        <f>0.13*F264</f>
+        <v>799760</v>
       </c>
       <c r="H264">
-        <v>163067</v>
+        <v>346000</v>
       </c>
       <c r="I264">
-        <v>88455</v>
+        <f>0.13*H264</f>
+        <v>44980</v>
+      </c>
+      <c r="J264">
+        <v>1</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.25">
@@ -9535,11 +9559,11 @@
         <v>12</v>
       </c>
       <c r="B265">
-        <f t="shared" ref="B265:B312" si="25">YEAR(C265)</f>
+        <f t="shared" si="20"/>
         <v>1996</v>
       </c>
       <c r="C265" s="2">
-        <v>35388</v>
+        <v>35268</v>
       </c>
       <c r="D265" s="4">
         <f t="shared" si="21"/>
@@ -9550,16 +9574,16 @@
         <v>1994</v>
       </c>
       <c r="F265">
-        <v>4471744</v>
+        <v>7258271</v>
       </c>
       <c r="G265" s="9">
-        <v>756874</v>
+        <v>1351084</v>
       </c>
       <c r="H265">
-        <v>1083062</v>
+        <v>163067</v>
       </c>
       <c r="I265">
-        <v>253372</v>
+        <v>88455</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.25">
@@ -9567,11 +9591,11 @@
         <v>12</v>
       </c>
       <c r="B266">
-        <f t="shared" si="25"/>
-        <v>1997</v>
+        <f t="shared" ref="B266:B313" si="25">YEAR(C266)</f>
+        <v>1996</v>
       </c>
       <c r="C266" s="2">
-        <v>35487</v>
+        <v>35388</v>
       </c>
       <c r="D266" s="4">
         <f t="shared" si="21"/>
@@ -9582,21 +9606,16 @@
         <v>1994</v>
       </c>
       <c r="F266">
-        <v>4761000</v>
+        <v>4471744</v>
       </c>
       <c r="G266" s="9">
-        <f>0.13*F266</f>
-        <v>618930</v>
+        <v>756874</v>
       </c>
       <c r="H266">
-        <v>31000</v>
+        <v>1083062</v>
       </c>
       <c r="I266">
-        <f>0.13*H266</f>
-        <v>4030</v>
-      </c>
-      <c r="J266">
-        <v>1</v>
+        <v>253372</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.25">
@@ -9608,29 +9627,29 @@
         <v>1997</v>
       </c>
       <c r="C267" s="2">
-        <v>35753</v>
+        <v>35487</v>
       </c>
       <c r="D267" s="4">
         <f t="shared" si="21"/>
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="E267" s="4">
         <f t="shared" si="22"/>
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="F267">
-        <v>18123000</v>
+        <v>4761000</v>
       </c>
       <c r="G267" s="9">
         <f>0.13*F267</f>
-        <v>2355990</v>
+        <v>618930</v>
       </c>
       <c r="H267">
-        <v>648000</v>
+        <v>31000</v>
       </c>
       <c r="I267">
         <f>0.13*H267</f>
-        <v>84240</v>
+        <v>4030</v>
       </c>
       <c r="J267">
         <v>1</v>
@@ -9642,10 +9661,10 @@
       </c>
       <c r="B268">
         <f t="shared" si="25"/>
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="C268" s="2">
-        <v>35859</v>
+        <v>35753</v>
       </c>
       <c r="D268" s="4">
         <f t="shared" si="21"/>
@@ -9656,18 +9675,21 @@
         <v>1995</v>
       </c>
       <c r="F268">
-        <v>8515000</v>
+        <v>18123000</v>
       </c>
       <c r="G268" s="9">
-        <f>0.18*F268</f>
-        <v>1532700</v>
+        <f>0.13*F268</f>
+        <v>2355990</v>
       </c>
       <c r="H268">
-        <v>49000</v>
+        <v>648000</v>
       </c>
       <c r="I268">
-        <f>0.18*H268</f>
-        <v>8820</v>
+        <f>0.13*H268</f>
+        <v>84240</v>
+      </c>
+      <c r="J268">
+        <v>1</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.25">
@@ -9679,29 +9701,29 @@
         <v>1998</v>
       </c>
       <c r="C269" s="2">
-        <v>36007</v>
+        <v>35859</v>
       </c>
       <c r="D269" s="4">
         <f t="shared" si="21"/>
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="E269" s="4">
         <f t="shared" si="22"/>
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="F269">
-        <v>9573000</v>
+        <v>8515000</v>
       </c>
       <c r="G269" s="9">
-        <f>0.24*F269</f>
-        <v>2297520</v>
+        <f>0.18*F269</f>
+        <v>1532700</v>
       </c>
       <c r="H269">
-        <v>22000</v>
+        <v>49000</v>
       </c>
       <c r="I269">
-        <f>0.24*H269</f>
-        <v>5280</v>
+        <f>0.18*H269</f>
+        <v>8820</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.25">
@@ -9713,7 +9735,7 @@
         <v>1998</v>
       </c>
       <c r="C270" s="2">
-        <v>36130</v>
+        <v>36007</v>
       </c>
       <c r="D270" s="4">
         <f t="shared" si="21"/>
@@ -9724,20 +9746,18 @@
         <v>1996</v>
       </c>
       <c r="F270">
-        <v>8233000</v>
+        <v>9573000</v>
       </c>
       <c r="G270" s="9">
-        <f>0.09*F270</f>
-        <v>740970</v>
+        <f>0.24*F270</f>
+        <v>2297520</v>
       </c>
       <c r="H270">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="I270">
-        <v>0</v>
-      </c>
-      <c r="J270">
-        <v>1</v>
+        <f>0.24*H270</f>
+        <v>5280</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.25">
@@ -9746,25 +9766,34 @@
       </c>
       <c r="B271">
         <f t="shared" si="25"/>
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="C271" s="2">
-        <v>36338</v>
+        <v>36130</v>
       </c>
       <c r="D271" s="4">
-        <f t="shared" ref="D271:D272" si="26">IF(MONTH(C271)&lt;4,B271-2,B271-1)</f>
-        <v>1998</v>
+        <f t="shared" si="21"/>
+        <v>1997</v>
       </c>
       <c r="E271" s="4">
-        <f t="shared" ref="E271:E272" si="27">IF(MONTH(C271)&lt;4,B271-3,B271-2)</f>
-        <v>1997</v>
+        <f t="shared" si="22"/>
+        <v>1996</v>
       </c>
       <c r="F271">
-        <v>5386000</v>
+        <v>8233000</v>
       </c>
       <c r="G271" s="9">
-        <f>0.29*F271</f>
-        <v>1561940</v>
+        <f>0.09*F271</f>
+        <v>740970</v>
+      </c>
+      <c r="H271">
+        <v>0</v>
+      </c>
+      <c r="I271">
+        <v>0</v>
+      </c>
+      <c r="J271">
+        <v>1</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.25">
@@ -9776,22 +9805,22 @@
         <v>1999</v>
       </c>
       <c r="C272" s="2">
-        <v>36362</v>
+        <v>36338</v>
       </c>
       <c r="D272" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="D272:D273" si="26">IF(MONTH(C272)&lt;4,B272-2,B272-1)</f>
         <v>1998</v>
       </c>
       <c r="E272" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="E272:E273" si="27">IF(MONTH(C272)&lt;4,B272-3,B272-2)</f>
         <v>1997</v>
       </c>
       <c r="F272">
-        <v>7141000</v>
+        <v>5386000</v>
       </c>
       <c r="G272" s="9">
-        <f>0.25*F272</f>
-        <v>1785250</v>
+        <f>0.29*F272</f>
+        <v>1561940</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.25">
@@ -9803,31 +9832,22 @@
         <v>1999</v>
       </c>
       <c r="C273" s="2">
-        <v>36494</v>
+        <v>36362</v>
       </c>
       <c r="D273" s="4">
-        <f t="shared" ref="D273:D312" si="28">IF(MONTH(C273)&lt;4,B273-2,B273-1)</f>
+        <f t="shared" si="26"/>
         <v>1998</v>
       </c>
       <c r="E273" s="4">
-        <f t="shared" ref="E273:E312" si="29">IF(MONTH(C273)&lt;4,B273-3,B273-2)</f>
+        <f t="shared" si="27"/>
         <v>1997</v>
       </c>
       <c r="F273">
-        <v>8462000</v>
+        <v>7141000</v>
       </c>
       <c r="G273" s="9">
-        <f>0.12*F273</f>
-        <v>1015440</v>
-      </c>
-      <c r="H273">
-        <v>0</v>
-      </c>
-      <c r="I273">
-        <v>0</v>
-      </c>
-      <c r="J273">
-        <v>1</v>
+        <f>0.25*F273</f>
+        <v>1785250</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.25">
@@ -9836,25 +9856,25 @@
       </c>
       <c r="B274">
         <f t="shared" si="25"/>
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="C274" s="2">
-        <v>36858</v>
+        <v>36494</v>
       </c>
       <c r="D274" s="4">
-        <f t="shared" si="28"/>
-        <v>1999</v>
+        <f t="shared" ref="D274:D313" si="28">IF(MONTH(C274)&lt;4,B274-2,B274-1)</f>
+        <v>1998</v>
       </c>
       <c r="E274" s="4">
-        <f t="shared" si="29"/>
-        <v>1998</v>
+        <f t="shared" ref="E274:E313" si="29">IF(MONTH(C274)&lt;4,B274-3,B274-2)</f>
+        <v>1997</v>
       </c>
       <c r="F274">
-        <v>9679000</v>
+        <v>8462000</v>
       </c>
       <c r="G274" s="9">
-        <f>0.15*F274</f>
-        <v>1451850</v>
+        <f>0.12*F274</f>
+        <v>1015440</v>
       </c>
       <c r="H274">
         <v>0</v>
@@ -9872,32 +9892,31 @@
       </c>
       <c r="B275">
         <f t="shared" si="25"/>
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C275" s="2">
-        <v>37230</v>
+        <v>36858</v>
       </c>
       <c r="D275" s="4">
         <f t="shared" si="28"/>
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="E275" s="4">
         <f t="shared" si="29"/>
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="F275">
-        <v>7478000</v>
+        <v>9679000</v>
       </c>
       <c r="G275" s="9">
-        <f>0.14*F275</f>
-        <v>1046920.0000000001</v>
+        <f>0.15*F275</f>
+        <v>1451850</v>
       </c>
       <c r="H275">
-        <v>326000</v>
+        <v>0</v>
       </c>
       <c r="I275">
-        <f>0.14*H275</f>
-        <v>45640.000000000007</v>
+        <v>0</v>
       </c>
       <c r="J275">
         <v>1</v>
@@ -9908,51 +9927,52 @@
         <v>12</v>
       </c>
       <c r="B276">
-        <v>2002</v>
+        <f t="shared" si="25"/>
+        <v>2001</v>
+      </c>
+      <c r="C276" s="2">
+        <v>37230</v>
       </c>
       <c r="D276" s="4">
-        <v>2001</v>
+        <f t="shared" si="28"/>
+        <v>2000</v>
       </c>
       <c r="E276" s="4">
-        <v>2000</v>
-      </c>
-      <c r="G276" s="9"/>
+        <f t="shared" si="29"/>
+        <v>1999</v>
+      </c>
+      <c r="F276">
+        <v>7478000</v>
+      </c>
+      <c r="G276" s="9">
+        <f>0.14*F276</f>
+        <v>1046920.0000000001</v>
+      </c>
+      <c r="H276">
+        <v>326000</v>
+      </c>
+      <c r="I276">
+        <f>0.14*H276</f>
+        <v>45640.000000000007</v>
+      </c>
+      <c r="J276">
+        <v>1</v>
+      </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>12</v>
       </c>
       <c r="B277">
-        <f t="shared" si="25"/>
-        <v>2003</v>
-      </c>
-      <c r="C277" s="2">
-        <v>37637</v>
+        <v>2002</v>
       </c>
       <c r="D277" s="4">
-        <f t="shared" si="28"/>
         <v>2001</v>
       </c>
       <c r="E277" s="4">
-        <f t="shared" si="29"/>
         <v>2000</v>
       </c>
-      <c r="F277">
-        <v>4773000</v>
-      </c>
-      <c r="G277" s="9">
-        <f>0.16*F277</f>
-        <v>763680</v>
-      </c>
-      <c r="H277">
-        <v>0</v>
-      </c>
-      <c r="I277">
-        <v>0</v>
-      </c>
-      <c r="J277">
-        <v>1</v>
-      </c>
+      <c r="G277" s="9"/>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
@@ -9960,24 +9980,25 @@
       </c>
       <c r="B278">
         <f t="shared" si="25"/>
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C278" s="2">
-        <v>38005</v>
+        <v>37637</v>
       </c>
       <c r="D278" s="4">
         <f t="shared" si="28"/>
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="E278" s="4">
         <f t="shared" si="29"/>
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="F278">
-        <v>8636807</v>
+        <v>4773000</v>
       </c>
       <c r="G278" s="9">
-        <v>1694839</v>
+        <f>0.16*F278</f>
+        <v>763680</v>
       </c>
       <c r="H278">
         <v>0</v>
@@ -9995,24 +10016,24 @@
       </c>
       <c r="B279">
         <f t="shared" si="25"/>
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="C279" s="2">
-        <v>38378</v>
+        <v>38005</v>
       </c>
       <c r="D279" s="4">
         <f t="shared" si="28"/>
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E279" s="4">
         <f t="shared" si="29"/>
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="F279">
-        <v>6703046</v>
+        <v>8636807</v>
       </c>
       <c r="G279" s="9">
-        <v>1052271</v>
+        <v>1694839</v>
       </c>
       <c r="H279">
         <v>0</v>
@@ -10030,24 +10051,24 @@
       </c>
       <c r="B280">
         <f t="shared" si="25"/>
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="C280" s="2">
-        <v>38721</v>
+        <v>38378</v>
       </c>
       <c r="D280" s="4">
         <f t="shared" si="28"/>
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="E280" s="4">
         <f t="shared" si="29"/>
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="F280">
-        <v>3525291</v>
-      </c>
-      <c r="G280">
-        <v>719392</v>
+        <v>6703046</v>
+      </c>
+      <c r="G280" s="9">
+        <v>1052271</v>
       </c>
       <c r="H280">
         <v>0</v>
@@ -10065,25 +10086,24 @@
       </c>
       <c r="B281">
         <f t="shared" si="25"/>
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C281" s="2">
-        <v>39120</v>
+        <v>38721</v>
       </c>
       <c r="D281" s="4">
         <f t="shared" si="28"/>
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="E281" s="4">
         <f t="shared" si="29"/>
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="F281">
-        <v>3660000</v>
+        <v>3525291</v>
       </c>
       <c r="G281">
-        <f>0.14*F281</f>
-        <v>512400.00000000006</v>
+        <v>719392</v>
       </c>
       <c r="H281">
         <v>0</v>
@@ -10104,29 +10124,28 @@
         <v>2007</v>
       </c>
       <c r="C282" s="2">
-        <v>39395</v>
+        <v>39120</v>
       </c>
       <c r="D282" s="4">
         <f t="shared" si="28"/>
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="E282" s="4">
         <f t="shared" si="29"/>
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="F282">
-        <v>5048000</v>
+        <v>3660000</v>
       </c>
       <c r="G282">
-        <f>0.18*F282</f>
-        <v>908640</v>
+        <f>0.14*F282</f>
+        <v>512400.00000000006</v>
       </c>
       <c r="H282">
-        <v>51000</v>
+        <v>0</v>
       </c>
       <c r="I282">
-        <f>0.18*H282</f>
-        <v>9180</v>
+        <v>0</v>
       </c>
       <c r="J282">
         <v>1</v>
@@ -10138,31 +10157,35 @@
       </c>
       <c r="B283">
         <f t="shared" si="25"/>
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="C283" s="2">
-        <v>39651</v>
+        <v>39395</v>
       </c>
       <c r="D283" s="4">
         <f t="shared" si="28"/>
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="E283" s="4">
         <f t="shared" si="29"/>
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="F283">
-        <v>5541000</v>
+        <v>5048000</v>
       </c>
       <c r="G283">
-        <f>0.28*F283</f>
-        <v>1551480.0000000002</v>
+        <f>0.18*F283</f>
+        <v>908640</v>
       </c>
       <c r="H283">
-        <v>0</v>
+        <v>51000</v>
       </c>
       <c r="I283">
-        <v>0</v>
+        <f>0.18*H283</f>
+        <v>9180</v>
+      </c>
+      <c r="J283">
+        <v>1</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.25">
@@ -10174,7 +10197,7 @@
         <v>2008</v>
       </c>
       <c r="C284" s="2">
-        <v>39769</v>
+        <v>39651</v>
       </c>
       <c r="D284" s="4">
         <f t="shared" si="28"/>
@@ -10185,20 +10208,17 @@
         <v>2006</v>
       </c>
       <c r="F284">
-        <v>6017000</v>
+        <v>5541000</v>
       </c>
       <c r="G284">
-        <f>0.16*F284</f>
-        <v>962720</v>
+        <f>0.28*F284</f>
+        <v>1551480.0000000002</v>
       </c>
       <c r="H284">
         <v>0</v>
       </c>
       <c r="I284">
         <v>0</v>
-      </c>
-      <c r="J284">
-        <v>1</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.25">
@@ -10210,7 +10230,7 @@
         <v>2008</v>
       </c>
       <c r="C285" s="2">
-        <v>39783</v>
+        <v>39769</v>
       </c>
       <c r="D285" s="4">
         <f t="shared" si="28"/>
@@ -10221,16 +10241,20 @@
         <v>2006</v>
       </c>
       <c r="F285">
-        <v>6017335</v>
+        <v>6017000</v>
       </c>
       <c r="G285">
-        <v>935967</v>
+        <f>0.16*F285</f>
+        <v>962720</v>
       </c>
       <c r="H285">
         <v>0</v>
       </c>
       <c r="I285">
         <v>0</v>
+      </c>
+      <c r="J285">
+        <v>1</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.25">
@@ -10239,25 +10263,24 @@
       </c>
       <c r="B286">
         <f t="shared" si="25"/>
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="C286" s="2">
-        <v>39973</v>
+        <v>39783</v>
       </c>
       <c r="D286" s="4">
         <f t="shared" si="28"/>
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="E286" s="4">
         <f t="shared" si="29"/>
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="F286">
-        <v>5540818</v>
+        <v>6017335</v>
       </c>
       <c r="G286">
-        <f>0.28*F286</f>
-        <v>1551429.04</v>
+        <v>935967</v>
       </c>
       <c r="H286">
         <v>0</v>
@@ -10275,7 +10298,7 @@
         <v>2009</v>
       </c>
       <c r="C287" s="2">
-        <v>40049</v>
+        <v>39973</v>
       </c>
       <c r="D287" s="4">
         <f t="shared" si="28"/>
@@ -10286,11 +10309,11 @@
         <v>2007</v>
       </c>
       <c r="F287">
-        <v>7596484</v>
+        <v>5540818</v>
       </c>
       <c r="G287">
-        <f>0.2*F287</f>
-        <v>1519296.8</v>
+        <f>0.28*F287</f>
+        <v>1551429.04</v>
       </c>
       <c r="H287">
         <v>0</v>
@@ -10308,7 +10331,7 @@
         <v>2009</v>
       </c>
       <c r="C288" s="2">
-        <v>40147</v>
+        <v>40049</v>
       </c>
       <c r="D288" s="4">
         <f t="shared" si="28"/>
@@ -10319,20 +10342,17 @@
         <v>2007</v>
       </c>
       <c r="F288">
-        <v>2450742</v>
+        <v>7596484</v>
       </c>
       <c r="G288">
-        <f>0.19*F288</f>
-        <v>465640.98</v>
+        <f>0.2*F288</f>
+        <v>1519296.8</v>
       </c>
       <c r="H288">
         <v>0</v>
       </c>
       <c r="I288">
         <v>0</v>
-      </c>
-      <c r="J288">
-        <v>1</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
@@ -10341,10 +10361,10 @@
       </c>
       <c r="B289">
         <f t="shared" si="25"/>
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="C289" s="2">
-        <v>40191</v>
+        <v>40147</v>
       </c>
       <c r="D289" s="4">
         <f t="shared" si="28"/>
@@ -10355,17 +10375,20 @@
         <v>2007</v>
       </c>
       <c r="F289">
-        <v>4979378</v>
+        <v>2450742</v>
       </c>
       <c r="G289">
-        <f>0.12*F289</f>
-        <v>597525.36</v>
+        <f>0.19*F289</f>
+        <v>465640.98</v>
       </c>
       <c r="H289">
         <v>0</v>
       </c>
       <c r="I289">
         <v>0</v>
+      </c>
+      <c r="J289">
+        <v>1</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
@@ -10377,21 +10400,22 @@
         <v>2010</v>
       </c>
       <c r="C290" s="2">
-        <v>40406</v>
+        <v>40191</v>
       </c>
       <c r="D290" s="4">
         <f t="shared" si="28"/>
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="E290" s="4">
         <f t="shared" si="29"/>
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="F290">
-        <v>16661391</v>
+        <v>4979378</v>
       </c>
       <c r="G290">
-        <v>5621822</v>
+        <f>0.12*F290</f>
+        <v>597525.36</v>
       </c>
       <c r="H290">
         <v>0</v>
@@ -10409,7 +10433,7 @@
         <v>2010</v>
       </c>
       <c r="C291" s="2">
-        <v>40414</v>
+        <v>40406</v>
       </c>
       <c r="D291" s="4">
         <f t="shared" si="28"/>
@@ -10420,10 +10444,10 @@
         <v>2008</v>
       </c>
       <c r="F291">
-        <v>8166458</v>
+        <v>16661391</v>
       </c>
       <c r="G291">
-        <v>2639773</v>
+        <v>5621822</v>
       </c>
       <c r="H291">
         <v>0</v>
@@ -10441,7 +10465,7 @@
         <v>2010</v>
       </c>
       <c r="C292" s="2">
-        <v>40512</v>
+        <v>40414</v>
       </c>
       <c r="D292" s="4">
         <f t="shared" si="28"/>
@@ -10452,20 +10476,16 @@
         <v>2008</v>
       </c>
       <c r="F292">
-        <v>14526189</v>
+        <v>8166458</v>
       </c>
       <c r="G292">
-        <f>0.24*F292</f>
-        <v>3486285.36</v>
+        <v>2639773</v>
       </c>
       <c r="H292">
         <v>0</v>
       </c>
       <c r="I292">
         <v>0</v>
-      </c>
-      <c r="J292">
-        <v>1</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.25">
@@ -10474,31 +10494,34 @@
       </c>
       <c r="B293">
         <f t="shared" si="25"/>
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C293" s="2">
-        <v>40771</v>
+        <v>40512</v>
       </c>
       <c r="D293" s="4">
         <f t="shared" si="28"/>
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="E293" s="4">
         <f t="shared" si="29"/>
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="F293">
-        <v>16661391</v>
+        <v>14526189</v>
       </c>
       <c r="G293">
-        <f>0.34*F293</f>
-        <v>5664872.9400000004</v>
+        <f>0.24*F293</f>
+        <v>3486285.36</v>
       </c>
       <c r="H293">
         <v>0</v>
       </c>
       <c r="I293">
         <v>0</v>
+      </c>
+      <c r="J293">
+        <v>1</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.25">
@@ -10510,7 +10533,7 @@
         <v>2011</v>
       </c>
       <c r="C294" s="2">
-        <v>40868</v>
+        <v>40771</v>
       </c>
       <c r="D294" s="4">
         <f t="shared" si="28"/>
@@ -10521,20 +10544,17 @@
         <v>2009</v>
       </c>
       <c r="F294">
-        <v>13444391</v>
+        <v>16661391</v>
       </c>
       <c r="G294">
-        <f>0.09*F294</f>
-        <v>1209995.19</v>
+        <f>0.34*F294</f>
+        <v>5664872.9400000004</v>
       </c>
       <c r="H294">
         <v>0</v>
       </c>
       <c r="I294">
         <v>0</v>
-      </c>
-      <c r="J294">
-        <v>1</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.25">
@@ -10543,30 +10563,34 @@
       </c>
       <c r="B295">
         <f t="shared" si="25"/>
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C295" s="2">
-        <v>41226</v>
+        <v>40868</v>
       </c>
       <c r="D295" s="4">
         <f t="shared" si="28"/>
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="E295" s="4">
         <f t="shared" si="29"/>
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="F295">
-        <v>14526189</v>
+        <v>13444391</v>
       </c>
       <c r="G295">
-        <v>2099030</v>
+        <f>0.09*F295</f>
+        <v>1209995.19</v>
       </c>
       <c r="H295">
-        <v>14526189</v>
+        <v>0</v>
       </c>
       <c r="I295">
-        <v>2099030</v>
+        <v>0</v>
+      </c>
+      <c r="J295">
+        <v>1</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.25">
@@ -10578,7 +10602,7 @@
         <v>2012</v>
       </c>
       <c r="C296" s="2">
-        <v>41073</v>
+        <v>41226</v>
       </c>
       <c r="D296" s="4">
         <f t="shared" si="28"/>
@@ -10589,16 +10613,16 @@
         <v>2010</v>
       </c>
       <c r="F296">
-        <v>15262441</v>
+        <v>14526189</v>
       </c>
       <c r="G296">
-        <v>5573233</v>
+        <v>2099030</v>
       </c>
       <c r="H296">
-        <v>0</v>
+        <v>14526189</v>
       </c>
       <c r="I296">
-        <v>0</v>
+        <v>2099030</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.25">
@@ -10610,7 +10634,7 @@
         <v>2012</v>
       </c>
       <c r="C297" s="2">
-        <v>41136</v>
+        <v>41073</v>
       </c>
       <c r="D297" s="4">
         <f t="shared" si="28"/>
@@ -10621,10 +10645,10 @@
         <v>2010</v>
       </c>
       <c r="F297">
-        <v>21862120</v>
+        <v>15262441</v>
       </c>
       <c r="G297">
-        <v>7651741.9999999991</v>
+        <v>5573233</v>
       </c>
       <c r="H297">
         <v>0</v>
@@ -10639,10 +10663,10 @@
       </c>
       <c r="B298">
         <f t="shared" si="25"/>
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C298" s="2">
-        <v>41331</v>
+        <v>41136</v>
       </c>
       <c r="D298" s="4">
         <f t="shared" si="28"/>
@@ -10653,20 +10677,16 @@
         <v>2010</v>
       </c>
       <c r="F298">
-        <v>14526189</v>
+        <v>21862120</v>
       </c>
       <c r="G298">
-        <f>0.14*F298</f>
-        <v>2033666.4600000002</v>
+        <v>7651741.9999999991</v>
       </c>
       <c r="H298">
         <v>0</v>
       </c>
       <c r="I298">
         <v>0</v>
-      </c>
-      <c r="J298">
-        <v>1</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
@@ -10678,28 +10698,31 @@
         <v>2013</v>
       </c>
       <c r="C299" s="2">
-        <v>41513</v>
+        <v>41331</v>
       </c>
       <c r="D299" s="4">
         <f t="shared" si="28"/>
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="E299" s="4">
         <f t="shared" si="29"/>
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="F299">
-        <v>11210000</v>
+        <v>14526189</v>
       </c>
       <c r="G299">
-        <f>0.21*F299</f>
-        <v>2354100</v>
+        <f>0.14*F299</f>
+        <v>2033666.4600000002</v>
       </c>
       <c r="H299">
         <v>0</v>
       </c>
       <c r="I299">
         <v>0</v>
+      </c>
+      <c r="J299">
+        <v>1</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.25">
@@ -10711,7 +10734,7 @@
         <v>2013</v>
       </c>
       <c r="C300" s="2">
-        <v>41597</v>
+        <v>41513</v>
       </c>
       <c r="D300" s="4">
         <f t="shared" si="28"/>
@@ -10722,20 +10745,17 @@
         <v>2011</v>
       </c>
       <c r="F300">
-        <v>3687000</v>
+        <v>11210000</v>
       </c>
       <c r="G300">
-        <f>0.31*F300</f>
-        <v>1142970</v>
+        <f>0.21*F300</f>
+        <v>2354100</v>
       </c>
       <c r="H300">
         <v>0</v>
       </c>
       <c r="I300">
         <v>0</v>
-      </c>
-      <c r="J300">
-        <v>1</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
@@ -10744,31 +10764,34 @@
       </c>
       <c r="B301">
         <f t="shared" si="25"/>
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C301" s="2">
-        <v>41932</v>
+        <v>41597</v>
       </c>
       <c r="D301" s="4">
         <f t="shared" si="28"/>
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="E301" s="4">
         <f t="shared" si="29"/>
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="F301">
-        <v>13157290</v>
+        <v>3687000</v>
       </c>
       <c r="G301">
-        <f>0.28*F301</f>
-        <v>3684041.2</v>
+        <f>0.31*F301</f>
+        <v>1142970</v>
       </c>
       <c r="H301">
         <v>0</v>
       </c>
       <c r="I301">
         <v>0</v>
+      </c>
+      <c r="J301">
+        <v>1</v>
       </c>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.25">
@@ -10777,10 +10800,10 @@
       </c>
       <c r="B302">
         <f t="shared" si="25"/>
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C302" s="2">
-        <v>42042</v>
+        <v>41932</v>
       </c>
       <c r="D302" s="4">
         <f t="shared" si="28"/>
@@ -10791,20 +10814,17 @@
         <v>2012</v>
       </c>
       <c r="F302">
-        <v>1210757</v>
+        <v>13157290</v>
       </c>
       <c r="G302">
-        <f>F302*0.23</f>
-        <v>278474.11</v>
+        <f>0.28*F302</f>
+        <v>3684041.2</v>
       </c>
       <c r="H302">
         <v>0</v>
       </c>
       <c r="I302">
         <v>0</v>
-      </c>
-      <c r="J302">
-        <v>1</v>
       </c>
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.25">
@@ -10816,22 +10836,22 @@
         <v>2015</v>
       </c>
       <c r="C303" s="2">
-        <v>42317</v>
+        <v>42042</v>
       </c>
       <c r="D303" s="4">
         <f t="shared" si="28"/>
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="E303" s="4">
         <f t="shared" si="29"/>
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="F303">
-        <v>4151619</v>
+        <v>1210757</v>
       </c>
       <c r="G303">
-        <f>0.3*F303</f>
-        <v>1245485.7</v>
+        <f>F303*0.23</f>
+        <v>278474.11</v>
       </c>
       <c r="H303">
         <v>0</v>
@@ -10849,10 +10869,10 @@
       </c>
       <c r="B304">
         <f t="shared" si="25"/>
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C304" s="2">
-        <v>42417</v>
+        <v>42317</v>
       </c>
       <c r="D304" s="4">
         <f t="shared" si="28"/>
@@ -10863,13 +10883,20 @@
         <v>2013</v>
       </c>
       <c r="F304">
-        <v>4150000</v>
+        <v>4151619</v>
+      </c>
+      <c r="G304">
+        <f>0.3*F304</f>
+        <v>1245485.7</v>
       </c>
       <c r="H304">
         <v>0</v>
       </c>
       <c r="I304">
         <v>0</v>
+      </c>
+      <c r="J304">
+        <v>1</v>
       </c>
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.25">
@@ -10881,30 +10908,24 @@
         <v>2016</v>
       </c>
       <c r="C305" s="2">
-        <v>42668</v>
+        <v>42417</v>
       </c>
       <c r="D305" s="4">
         <f t="shared" si="28"/>
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="E305" s="4">
         <f t="shared" si="29"/>
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="F305">
-        <v>5917285</v>
-      </c>
-      <c r="G305">
-        <v>1047465</v>
+        <v>4150000</v>
       </c>
       <c r="H305">
         <v>0</v>
       </c>
       <c r="I305">
         <v>0</v>
-      </c>
-      <c r="J305">
-        <v>1</v>
       </c>
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.25">
@@ -10913,31 +10934,33 @@
       </c>
       <c r="B306">
         <f t="shared" si="25"/>
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C306" s="2">
-        <v>43056</v>
+        <v>42668</v>
       </c>
       <c r="D306" s="4">
         <f t="shared" si="28"/>
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="E306" s="4">
         <f t="shared" si="29"/>
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="F306">
-        <v>6423238</v>
+        <v>5917285</v>
       </c>
       <c r="G306">
-        <f>(6823499-6022976)/1.28</f>
-        <v>625408.59375</v>
+        <v>1047465</v>
       </c>
       <c r="H306">
         <v>0</v>
       </c>
       <c r="I306">
         <v>0</v>
+      </c>
+      <c r="J306">
+        <v>1</v>
       </c>
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.25">
@@ -10946,10 +10969,10 @@
       </c>
       <c r="B307">
         <f t="shared" si="25"/>
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C307" s="2">
-        <v>43151</v>
+        <v>43056</v>
       </c>
       <c r="D307" s="4">
         <f t="shared" si="28"/>
@@ -10960,20 +10983,17 @@
         <v>2015</v>
       </c>
       <c r="F307">
-        <v>8422379</v>
+        <v>6423238</v>
       </c>
       <c r="G307">
-        <f>(8746816-8097942)/1.28</f>
-        <v>506932.8125</v>
+        <f>(6823499-6022976)/1.28</f>
+        <v>625408.59375</v>
       </c>
       <c r="H307">
         <v>0</v>
       </c>
       <c r="I307">
         <v>0</v>
-      </c>
-      <c r="J307">
-        <v>1</v>
       </c>
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.25">
@@ -10982,25 +11002,25 @@
       </c>
       <c r="B308">
         <f t="shared" si="25"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C308" s="2">
-        <v>43488</v>
+        <v>43151</v>
       </c>
       <c r="D308" s="4">
         <f t="shared" si="28"/>
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="E308" s="4">
         <f t="shared" si="29"/>
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="F308">
-        <v>1555655</v>
+        <v>8422379</v>
       </c>
       <c r="G308">
-        <f>(1633398-1477932)/1.28</f>
-        <v>121457.8125</v>
+        <f>(8746816-8097942)/1.28</f>
+        <v>506932.8125</v>
       </c>
       <c r="H308">
         <v>0</v>
@@ -11018,25 +11038,25 @@
       </c>
       <c r="B309">
         <f t="shared" si="25"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C309" s="2">
-        <v>43886</v>
+        <v>43488</v>
       </c>
       <c r="D309" s="4">
         <f t="shared" si="28"/>
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="E309" s="4">
         <f t="shared" si="29"/>
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="F309">
-        <v>3784000</v>
+        <v>1555655</v>
       </c>
       <c r="G309">
-        <f>(4243000-3362000)/1.96</f>
-        <v>449489.79591836734</v>
+        <f>(1633398-1477932)/1.28</f>
+        <v>121457.8125</v>
       </c>
       <c r="H309">
         <v>0</v>
@@ -11054,25 +11074,25 @@
       </c>
       <c r="B310">
         <f t="shared" si="25"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C310" s="2">
-        <v>44243</v>
+        <v>43886</v>
       </c>
       <c r="D310" s="4">
         <f t="shared" si="28"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="E310" s="4">
         <f t="shared" si="29"/>
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F310">
-        <v>1630000</v>
+        <v>3784000</v>
       </c>
       <c r="G310">
-        <f>0.1*F310</f>
-        <v>163000</v>
+        <f>(4243000-3362000)/1.96</f>
+        <v>449489.79591836734</v>
       </c>
       <c r="H310">
         <v>0</v>
@@ -11090,32 +11110,31 @@
       </c>
       <c r="B311">
         <f t="shared" si="25"/>
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C311" s="2">
-        <v>44593</v>
+        <v>44243</v>
       </c>
       <c r="D311" s="4">
         <f t="shared" si="28"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E311" s="4">
         <f t="shared" si="29"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="F311">
-        <v>2207921</v>
+        <v>1630000</v>
       </c>
       <c r="G311">
-        <f>(2432712-1999434)/1.96</f>
-        <v>221060.20408163266</v>
+        <f>0.1*F311</f>
+        <v>163000</v>
       </c>
       <c r="H311">
-        <v>16791</v>
+        <v>0</v>
       </c>
       <c r="I311">
-        <f>(18495-15205)/1.96</f>
-        <v>1678.5714285714287</v>
+        <v>0</v>
       </c>
       <c r="J311">
         <v>1</v>
@@ -11127,31 +11146,32 @@
       </c>
       <c r="B312">
         <f t="shared" si="25"/>
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C312" s="2">
-        <v>44970</v>
+        <v>44593</v>
       </c>
       <c r="D312" s="4">
         <f t="shared" si="28"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E312" s="4">
         <f t="shared" si="29"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="F312">
-        <v>1219678</v>
+        <v>2207921</v>
       </c>
       <c r="G312">
-        <f>(1343499-1104508)/1.96</f>
-        <v>121934.18367346939</v>
+        <f>(2432712-1999434)/1.96</f>
+        <v>221060.20408163266</v>
       </c>
       <c r="H312">
-        <v>0</v>
+        <v>16791</v>
       </c>
       <c r="I312">
-        <v>0</v>
+        <f>(18495-15205)/1.96</f>
+        <v>1678.5714285714287</v>
       </c>
       <c r="J312">
         <v>1</v>
@@ -11162,27 +11182,63 @@
         <v>12</v>
       </c>
       <c r="B313">
+        <f t="shared" si="25"/>
+        <v>2023</v>
+      </c>
+      <c r="C313" s="2">
+        <v>44970</v>
+      </c>
+      <c r="D313" s="4">
+        <f t="shared" si="28"/>
+        <v>2021</v>
+      </c>
+      <c r="E313" s="4">
+        <f t="shared" si="29"/>
+        <v>2020</v>
+      </c>
+      <c r="F313">
+        <v>1219678</v>
+      </c>
+      <c r="G313">
+        <f>(1343499-1104508)/1.96</f>
+        <v>121934.18367346939</v>
+      </c>
+      <c r="H313">
+        <v>0</v>
+      </c>
+      <c r="I313">
+        <v>0</v>
+      </c>
+      <c r="J313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>12</v>
+      </c>
+      <c r="B314">
         <v>2024</v>
       </c>
-      <c r="C313" s="2">
+      <c r="C314" s="2">
         <v>45357</v>
       </c>
-      <c r="D313" s="4">
-        <f>IF(MONTH(C313)&lt;4,B313-2,B313-1)</f>
+      <c r="D314" s="4">
+        <f>IF(MONTH(C314)&lt;4,B314-2,B314-1)</f>
         <v>2022</v>
       </c>
-      <c r="E313" s="4">
-        <f>IF(MONTH(C313)&lt;4,B313-3,B313-2)</f>
+      <c r="E314" s="4">
+        <f>IF(MONTH(C314)&lt;4,B314-3,B314-2)</f>
         <v>2021</v>
       </c>
-      <c r="F313">
+      <c r="F314">
         <v>1481384</v>
       </c>
-      <c r="G313">
+      <c r="G314">
         <f>(1642999-1331841)/1.96</f>
         <v>158754.08163265308</v>
       </c>
-      <c r="J313">
+      <c r="J314">
         <v>1</v>
       </c>
     </row>

--- a/1. data/Barkley-Sk_pre-smolt_abundances.xlsx
+++ b/1. data/Barkley-Sk_pre-smolt_abundances.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brownn\Documents\WCVI\Barkley-Sk-CSAS\1. data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3A6A23-78BD-405B-B0CD-A17B2BB718DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D15978-C998-47CB-8D46-540FE58618E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{93B9BABA-C468-4873-970E-7D7E9A90394F}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{93B9BABA-C468-4873-970E-7D7E9A90394F}"/>
   </bookViews>
   <sheets>
     <sheet name="ATS_estimates" sheetId="2" r:id="rId1"/>
@@ -44,6 +44,7 @@
   <authors>
     <author>tc={51828A2D-7DC2-4829-B811-13295E6A575B}</author>
     <author>Brown, Nicholas</author>
+    <author>tc={B04D9570-41A7-451D-9DD4-2694F69E80A1}</author>
     <author>tc={9450F348-AFEB-4317-AD43-51976EFBA421}</author>
     <author>tc={C335BF2D-8A76-4A85-B639-EC939DD5E53A}</author>
     <author>tc={3E6EE213-51C5-4BE7-94A1-C3C937E7343E}</author>
@@ -113,7 +114,15 @@
         </r>
       </text>
     </comment>
-    <comment ref="F113" authorId="2" shapeId="0" xr:uid="{9450F348-AFEB-4317-AD43-51976EFBA421}">
+    <comment ref="H109" authorId="2" shapeId="0" xr:uid="{B04D9570-41A7-451D-9DD4-2694F69E80A1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    3 out of 192 fish caught (1.56%) were sticklebacks</t>
+      </text>
+    </comment>
+    <comment ref="F113" authorId="3" shapeId="0" xr:uid="{9450F348-AFEB-4317-AD43-51976EFBA421}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -121,7 +130,7 @@
     From Howard Stiff via log-linear regression of total abundance versus smolt length (62mm in Nov 1979) in Hucuktlis Lake.</t>
       </text>
     </comment>
-    <comment ref="G113" authorId="3" shapeId="0" xr:uid="{C335BF2D-8A76-4A85-B639-EC939DD5E53A}">
+    <comment ref="G113" authorId="4" shapeId="0" xr:uid="{C335BF2D-8A76-4A85-B639-EC939DD5E53A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -129,7 +138,7 @@
     1977-1985 average CV applied to guesstimated mean</t>
       </text>
     </comment>
-    <comment ref="F211" authorId="4" shapeId="0" xr:uid="{3E6EE213-51C5-4BE7-94A1-C3C937E7343E}">
+    <comment ref="F211" authorId="5" shapeId="0" xr:uid="{3E6EE213-51C5-4BE7-94A1-C3C937E7343E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -137,7 +146,7 @@
     Assuming 50/50 Sk/Stickle. Tows caught 3 Sk, 6 Stickle, but notes indicate they likely hit a pocket of stickles at a shallower depth</t>
       </text>
     </comment>
-    <comment ref="G212" authorId="5" shapeId="0" xr:uid="{288476D4-5EF1-4853-B334-5E56430540C8}">
+    <comment ref="G212" authorId="6" shapeId="0" xr:uid="{288476D4-5EF1-4853-B334-5E56430540C8}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -145,7 +154,7 @@
     Converts 95% CI of the total limnetic fish estimate to a coefficient of variation, and then multiplies that by the species specific estimate to yield and SD value. </t>
       </text>
     </comment>
-    <comment ref="I212" authorId="6" shapeId="0" xr:uid="{FC5C3F1C-3F41-443B-A044-4AEECF017EAF}">
+    <comment ref="I212" authorId="7" shapeId="0" xr:uid="{FC5C3F1C-3F41-443B-A044-4AEECF017EAF}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -153,7 +162,7 @@
     Converts 95% CI of the total limnetic fish estimate to a coefficient of variation, and then multiplies that by the species specific estimate to yield and SD value. </t>
       </text>
     </comment>
-    <comment ref="G213" authorId="7" shapeId="0" xr:uid="{80809EA6-1C75-4782-B75F-9B8D8E1FF3DD}">
+    <comment ref="G213" authorId="8" shapeId="0" xr:uid="{80809EA6-1C75-4782-B75F-9B8D8E1FF3DD}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -162,7 +171,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="I213" authorId="8" shapeId="0" xr:uid="{4AD49B9C-A1D0-4A25-B5DF-3F2CF529CCE3}">
+    <comment ref="I213" authorId="9" shapeId="0" xr:uid="{4AD49B9C-A1D0-4A25-B5DF-3F2CF529CCE3}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -171,7 +180,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="G214" authorId="9" shapeId="0" xr:uid="{C9E6BF89-D9D3-4E3C-B697-A5DC0E655E3C}">
+    <comment ref="G214" authorId="10" shapeId="0" xr:uid="{C9E6BF89-D9D3-4E3C-B697-A5DC0E655E3C}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -180,7 +189,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="I214" authorId="10" shapeId="0" xr:uid="{30CBB802-82F2-45BB-8B27-7315D97962A6}">
+    <comment ref="I214" authorId="11" shapeId="0" xr:uid="{30CBB802-82F2-45BB-8B27-7315D97962A6}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -189,7 +198,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="G215" authorId="11" shapeId="0" xr:uid="{1FC59F05-C26A-4351-8236-C828500ADDBC}">
+    <comment ref="G215" authorId="12" shapeId="0" xr:uid="{1FC59F05-C26A-4351-8236-C828500ADDBC}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -198,7 +207,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="I215" authorId="12" shapeId="0" xr:uid="{1348B42C-4137-429B-A693-D62CB5C3BC03}">
+    <comment ref="I215" authorId="13" shapeId="0" xr:uid="{1348B42C-4137-429B-A693-D62CB5C3BC03}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -309,7 +318,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -351,12 +360,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -723,6 +726,9 @@
   <threadedComment ref="G1" dT="2025-02-07T20:07:08.24" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{51828A2D-7DC2-4829-B811-13295E6A575B}">
     <text xml:space="preserve">SD? =sqrt(sum(transect variances)/N transects) </text>
   </threadedComment>
+  <threadedComment ref="H109" dT="2026-04-23T16:57:34.95" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{B04D9570-41A7-451D-9DD4-2694F69E80A1}">
+    <text>3 out of 192 fish caught (1.56%) were sticklebacks</text>
+  </threadedComment>
   <threadedComment ref="F113" dT="2025-03-04T16:49:42.59" personId="{3DE5C77A-2EC9-410D-AF92-25A6BD2452F6}" id="{9450F348-AFEB-4317-AD43-51976EFBA421}">
     <text>From Howard Stiff via log-linear regression of total abundance versus smolt length (62mm in Nov 1979) in Hucuktlis Lake.</text>
   </threadedComment>
@@ -768,19 +774,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47CDFEE8-69FE-4C98-AD8C-E5081C486B0D}">
   <dimension ref="A1:J314"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.109375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>10</v>
       </c>
@@ -812,7 +818,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -844,7 +850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -879,7 +885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -911,7 +917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -943,7 +949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -978,7 +984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1010,7 +1016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1042,7 +1048,7 @@
         <v>867502</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1074,7 +1080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1111,7 +1117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1143,7 +1149,7 @@
         <v>1105842</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1179,7 +1185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1211,7 +1217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -1243,7 +1249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -1279,7 +1285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -1311,7 +1317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -1343,7 +1349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -1378,7 +1384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -1410,7 +1416,7 @@
         <v>149117</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -1442,7 +1448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -1477,7 +1483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -1512,7 +1518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -1547,7 +1553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -1579,7 +1585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -1614,7 +1620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -1646,7 +1652,7 @@
         <v>70186</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1678,7 +1684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -1713,7 +1719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -1748,7 +1754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -1780,7 +1786,7 @@
         <v>400080</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -1815,7 +1821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -1847,7 +1853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -1879,7 +1885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -1911,7 +1917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -1943,7 +1949,7 @@
         <v>5249683</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -1975,7 +1981,7 @@
         <v>5292344</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -2007,7 +2013,7 @@
         <v>4668519</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>11</v>
       </c>
@@ -2039,7 +2045,7 @@
         <v>4487517</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>11</v>
       </c>
@@ -2076,7 +2082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>11</v>
       </c>
@@ -2108,7 +2114,7 @@
         <v>846068</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>11</v>
       </c>
@@ -2140,7 +2146,7 @@
         <v>2376569</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>11</v>
       </c>
@@ -2175,7 +2181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>11</v>
       </c>
@@ -2207,7 +2213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>11</v>
       </c>
@@ -2239,7 +2245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>11</v>
       </c>
@@ -2274,7 +2280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>11</v>
       </c>
@@ -2306,7 +2312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -2338,7 +2344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>11</v>
       </c>
@@ -2370,7 +2376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>11</v>
       </c>
@@ -2405,7 +2411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>11</v>
       </c>
@@ -2437,7 +2443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>11</v>
       </c>
@@ -2469,7 +2475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>11</v>
       </c>
@@ -2501,7 +2507,7 @@
         <v>534137</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>11</v>
       </c>
@@ -2536,7 +2542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>11</v>
       </c>
@@ -2568,7 +2574,7 @@
         <v>210812</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>11</v>
       </c>
@@ -2600,7 +2606,7 @@
         <v>6591475</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -2632,7 +2638,7 @@
         <v>304743</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>11</v>
       </c>
@@ -2667,7 +2673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>11</v>
       </c>
@@ -2699,7 +2705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>11</v>
       </c>
@@ -2731,7 +2737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>11</v>
       </c>
@@ -2766,7 +2772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>11</v>
       </c>
@@ -2800,7 +2806,7 @@
         <v>326300</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>11</v>
       </c>
@@ -2834,7 +2840,7 @@
         <v>16820</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -2870,7 +2876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>11</v>
       </c>
@@ -2903,7 +2909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>11</v>
       </c>
@@ -2940,7 +2946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>11</v>
       </c>
@@ -2973,7 +2979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>11</v>
       </c>
@@ -3007,7 +3013,7 @@
         <v>31360</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>11</v>
       </c>
@@ -3042,7 +3048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>11</v>
       </c>
@@ -3078,7 +3084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>11</v>
       </c>
@@ -3114,7 +3120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>11</v>
       </c>
@@ -3130,7 +3136,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>11</v>
       </c>
@@ -3166,7 +3172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>11</v>
       </c>
@@ -3202,7 +3208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>11</v>
       </c>
@@ -3237,7 +3243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>11</v>
       </c>
@@ -3253,7 +3259,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>11</v>
       </c>
@@ -3289,7 +3295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>11</v>
       </c>
@@ -3324,7 +3330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>11</v>
       </c>
@@ -3359,7 +3365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>11</v>
       </c>
@@ -3391,7 +3397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>11</v>
       </c>
@@ -3426,7 +3432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>11</v>
       </c>
@@ -3458,7 +3464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>11</v>
       </c>
@@ -3485,7 +3491,7 @@
         <v>4226789.28</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>11</v>
       </c>
@@ -3512,7 +3518,7 @@
         <v>7833591.3599999994</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>11</v>
       </c>
@@ -3542,7 +3548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>11</v>
       </c>
@@ -3568,7 +3574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>11</v>
       </c>
@@ -3600,7 +3606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>11</v>
       </c>
@@ -3635,7 +3641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>11</v>
       </c>
@@ -3667,7 +3673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>11</v>
       </c>
@@ -3702,7 +3708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>11</v>
       </c>
@@ -3734,7 +3740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>11</v>
       </c>
@@ -3766,7 +3772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>11</v>
       </c>
@@ -3801,7 +3807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>11</v>
       </c>
@@ -3833,7 +3839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>11</v>
       </c>
@@ -3866,7 +3872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>11</v>
       </c>
@@ -3902,7 +3908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>11</v>
       </c>
@@ -3934,7 +3940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>11</v>
       </c>
@@ -3963,7 +3969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>11</v>
       </c>
@@ -3992,7 +3998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>11</v>
       </c>
@@ -4021,7 +4027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>11</v>
       </c>
@@ -4048,7 +4054,7 @@
         <v>1526020.4081632653</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>11</v>
       </c>
@@ -4078,7 +4084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>11</v>
       </c>
@@ -4098,7 +4104,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>11</v>
       </c>
@@ -4128,7 +4134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>11</v>
       </c>
@@ -4158,7 +4164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>11</v>
       </c>
@@ -4185,7 +4191,7 @@
         <v>121457.8125</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -4221,7 +4227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -4257,7 +4263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -4293,7 +4299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>11</v>
       </c>
@@ -4311,18 +4317,27 @@
         <f>IF(MONTH(C109)&lt;4,B109-3,B109-2)</f>
         <v>2021</v>
       </c>
-      <c r="F109">
-        <v>4473417</v>
+      <c r="F109" s="4">
+        <f>4473417*(1-0.0156)</f>
+        <v>4403631.6948000006</v>
       </c>
       <c r="G109">
         <f>(4903172-4072181)/1.96</f>
         <v>423975</v>
       </c>
+      <c r="H109" s="4">
+        <f>4473417*0.0156</f>
+        <v>69785.305200000003</v>
+      </c>
+      <c r="I109" s="4">
+        <f>(G109/F109)*H109</f>
+        <v>6718.8236489232013</v>
+      </c>
       <c r="J109">
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>13</v>
       </c>
@@ -4354,7 +4369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>13</v>
       </c>
@@ -4389,7 +4404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>13</v>
       </c>
@@ -4426,7 +4441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>13</v>
       </c>
@@ -4456,7 +4471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>13</v>
       </c>
@@ -4488,7 +4503,7 @@
         <v>450219</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>13</v>
       </c>
@@ -4525,7 +4540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>13</v>
       </c>
@@ -4557,7 +4572,7 @@
         <v>879281</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>13</v>
       </c>
@@ -4589,7 +4604,7 @@
         <v>337552</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>13</v>
       </c>
@@ -4624,7 +4639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>13</v>
       </c>
@@ -4656,7 +4671,7 @@
         <v>344340</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>13</v>
       </c>
@@ -4688,7 +4703,7 @@
         <v>170713</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>13</v>
       </c>
@@ -4720,7 +4735,7 @@
         <v>24295</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>13</v>
       </c>
@@ -4757,7 +4772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>13</v>
       </c>
@@ -4789,7 +4804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>13</v>
       </c>
@@ -4821,7 +4836,7 @@
         <v>751732</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>13</v>
       </c>
@@ -4856,7 +4871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>13</v>
       </c>
@@ -4888,7 +4903,7 @@
         <v>131280</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>13</v>
       </c>
@@ -4923,7 +4938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>13</v>
       </c>
@@ -4955,7 +4970,7 @@
         <v>119280</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>13</v>
       </c>
@@ -4992,7 +5007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>13</v>
       </c>
@@ -5024,7 +5039,7 @@
         <v>105083</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>13</v>
       </c>
@@ -5056,7 +5071,7 @@
         <v>82242</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>13</v>
       </c>
@@ -5088,7 +5103,7 @@
         <v>655143</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>13</v>
       </c>
@@ -5120,7 +5135,7 @@
         <v>1740864</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>13</v>
       </c>
@@ -5157,7 +5172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>13</v>
       </c>
@@ -5189,7 +5204,7 @@
         <v>695731</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>13</v>
       </c>
@@ -5226,7 +5241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>13</v>
       </c>
@@ -5258,7 +5273,7 @@
         <v>1289216</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>13</v>
       </c>
@@ -5290,7 +5305,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>13</v>
       </c>
@@ -5327,7 +5342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>13</v>
       </c>
@@ -5359,7 +5374,7 @@
         <v>206841</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>13</v>
       </c>
@@ -5391,7 +5406,7 @@
         <v>24280</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>13</v>
       </c>
@@ -5428,7 +5443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>13</v>
       </c>
@@ -5460,7 +5475,7 @@
         <v>488319</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>13</v>
       </c>
@@ -5497,7 +5512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>13</v>
       </c>
@@ -5529,7 +5544,7 @@
         <v>165938</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>13</v>
       </c>
@@ -5561,7 +5576,7 @@
         <v>380799</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>13</v>
       </c>
@@ -5598,7 +5613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>13</v>
       </c>
@@ -5630,7 +5645,7 @@
         <v>52821</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>13</v>
       </c>
@@ -5662,7 +5677,7 @@
         <v>1310377</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>13</v>
       </c>
@@ -5699,7 +5714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>13</v>
       </c>
@@ -5731,7 +5746,7 @@
         <v>285541</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>13</v>
       </c>
@@ -5763,7 +5778,7 @@
         <v>15483</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>13</v>
       </c>
@@ -5795,7 +5810,7 @@
         <v>5609</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>13</v>
       </c>
@@ -5827,7 +5842,7 @@
         <v>893130</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>13</v>
       </c>
@@ -5864,7 +5879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>13</v>
       </c>
@@ -5896,7 +5911,7 @@
         <v>14758</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>13</v>
       </c>
@@ -5928,7 +5943,7 @@
         <v>14502</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>13</v>
       </c>
@@ -5960,7 +5975,7 @@
         <v>24193</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>13</v>
       </c>
@@ -5997,7 +6012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>13</v>
       </c>
@@ -6029,7 +6044,7 @@
         <v>30347</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>13</v>
       </c>
@@ -6061,7 +6076,7 @@
         <v>75839</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>13</v>
       </c>
@@ -6093,7 +6108,7 @@
         <v>36419</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>13</v>
       </c>
@@ -6125,7 +6140,7 @@
         <v>87893</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>13</v>
       </c>
@@ -6160,7 +6175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>13</v>
       </c>
@@ -6192,7 +6207,7 @@
         <v>539162</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>13</v>
       </c>
@@ -6224,7 +6239,7 @@
         <v>471845</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>13</v>
       </c>
@@ -6256,7 +6271,7 @@
         <v>313811</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>13</v>
       </c>
@@ -6288,7 +6303,7 @@
         <v>314306</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>13</v>
       </c>
@@ -6325,7 +6340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>13</v>
       </c>
@@ -6358,7 +6373,7 @@
         <v>13490</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>13</v>
       </c>
@@ -6391,7 +6406,7 @@
         <v>22010</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>13</v>
       </c>
@@ -6427,7 +6442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>13</v>
       </c>
@@ -6460,7 +6475,7 @@
         <v>63600</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>13</v>
       </c>
@@ -6493,7 +6508,7 @@
         <v>97400</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>13</v>
       </c>
@@ -6529,7 +6544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>13</v>
       </c>
@@ -6565,7 +6580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>13</v>
       </c>
@@ -6598,7 +6613,7 @@
         <v>11760.000000000002</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>13</v>
       </c>
@@ -6631,7 +6646,7 @@
         <v>22960.000000000004</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>13</v>
       </c>
@@ -6667,7 +6682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>13</v>
       </c>
@@ -6703,7 +6718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>13</v>
       </c>
@@ -6738,7 +6753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>13</v>
       </c>
@@ -6775,7 +6790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>13</v>
       </c>
@@ -6812,7 +6827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>13</v>
       </c>
@@ -6846,7 +6861,7 @@
         <v>66640</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>13</v>
       </c>
@@ -6880,7 +6895,7 @@
         <v>27540</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>13</v>
       </c>
@@ -6914,7 +6929,7 @@
         <v>120650</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>13</v>
       </c>
@@ -6951,7 +6966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>13</v>
       </c>
@@ -6985,7 +7000,7 @@
         <v>66650</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>13</v>
       </c>
@@ -7019,7 +7034,7 @@
         <v>207740</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>13</v>
       </c>
@@ -7053,7 +7068,7 @@
         <v>127820</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>13</v>
       </c>
@@ -7088,7 +7103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>13</v>
       </c>
@@ -7120,7 +7135,7 @@
         <v>270240</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>13</v>
       </c>
@@ -7152,7 +7167,7 @@
         <v>291510</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>13</v>
       </c>
@@ -7187,7 +7202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>13</v>
       </c>
@@ -7220,7 +7235,7 @@
         <v>555100</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>13</v>
       </c>
@@ -7253,7 +7268,7 @@
         <v>283360</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>13</v>
       </c>
@@ -7290,7 +7305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>13</v>
       </c>
@@ -7324,7 +7339,7 @@
         <v>429049</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>13</v>
       </c>
@@ -7361,7 +7376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>13</v>
       </c>
@@ -7395,7 +7410,7 @@
         <v>204044.73</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>13</v>
       </c>
@@ -7432,7 +7447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>13</v>
       </c>
@@ -7467,7 +7482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>13</v>
       </c>
@@ -7501,7 +7516,7 @@
         <v>63978.390000000007</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>13</v>
       </c>
@@ -7533,7 +7548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>13</v>
       </c>
@@ -7570,7 +7585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>13</v>
       </c>
@@ -7604,7 +7619,7 @@
         <v>442446.89999999997</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>13</v>
       </c>
@@ -7641,7 +7656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>13</v>
       </c>
@@ -7675,7 +7690,7 @@
         <v>341621.7</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>13</v>
       </c>
@@ -7712,7 +7727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>13</v>
       </c>
@@ -7749,7 +7764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>13</v>
       </c>
@@ -7787,7 +7802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>13</v>
       </c>
@@ -7824,7 +7839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>13</v>
       </c>
@@ -7858,7 +7873,7 @@
         <v>54632.269399307814</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>13</v>
       </c>
@@ -7895,7 +7910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>13</v>
       </c>
@@ -7932,7 +7947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>12</v>
       </c>
@@ -7967,7 +7982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>12</v>
       </c>
@@ -8002,7 +8017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>12</v>
       </c>
@@ -8034,7 +8049,7 @@
         <v>36969</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>12</v>
       </c>
@@ -8066,7 +8081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>12</v>
       </c>
@@ -8101,7 +8116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>12</v>
       </c>
@@ -8133,7 +8148,7 @@
         <v>212426</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>12</v>
       </c>
@@ -8165,7 +8180,7 @@
         <v>137604</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>12</v>
       </c>
@@ -8200,7 +8215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>12</v>
       </c>
@@ -8232,7 +8247,7 @@
         <v>5826</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>12</v>
       </c>
@@ -8267,7 +8282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>12</v>
       </c>
@@ -8302,7 +8317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>12</v>
       </c>
@@ -8337,7 +8352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>12</v>
       </c>
@@ -8369,7 +8384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>12</v>
       </c>
@@ -8401,7 +8416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>12</v>
       </c>
@@ -8433,7 +8448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>12</v>
       </c>
@@ -8468,7 +8483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>12</v>
       </c>
@@ -8500,7 +8515,7 @@
         <v>78489</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>12</v>
       </c>
@@ -8532,7 +8547,7 @@
         <v>14564</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>12</v>
       </c>
@@ -8564,7 +8579,7 @@
         <v>41137</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>12</v>
       </c>
@@ -8599,7 +8614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>12</v>
       </c>
@@ -8634,7 +8649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>12</v>
       </c>
@@ -8666,7 +8681,7 @@
         <v>310981</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>12</v>
       </c>
@@ -8701,7 +8716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>12</v>
       </c>
@@ -8733,7 +8748,7 @@
         <v>11020</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>12</v>
       </c>
@@ -8765,7 +8780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>12</v>
       </c>
@@ -8797,7 +8812,7 @@
         <v>293891</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>12</v>
       </c>
@@ -8829,7 +8844,7 @@
         <v>360976</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>12</v>
       </c>
@@ -8861,7 +8876,7 @@
         <v>391872</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>12</v>
       </c>
@@ -8893,7 +8908,7 @@
         <v>659443</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>12</v>
       </c>
@@ -8925,7 +8940,7 @@
         <v>360135</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>12</v>
       </c>
@@ -8957,7 +8972,7 @@
         <v>607388</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>12</v>
       </c>
@@ -8989,7 +9004,7 @@
         <v>445150</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>12</v>
       </c>
@@ -9024,7 +9039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>12</v>
       </c>
@@ -9056,7 +9071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>12</v>
       </c>
@@ -9088,7 +9103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>12</v>
       </c>
@@ -9123,7 +9138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>12</v>
       </c>
@@ -9155,7 +9170,7 @@
         <v>252918</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>12</v>
       </c>
@@ -9187,7 +9202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>12</v>
       </c>
@@ -9222,7 +9237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>12</v>
       </c>
@@ -9254,7 +9269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>12</v>
       </c>
@@ -9286,7 +9301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>12</v>
       </c>
@@ -9321,7 +9336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>12</v>
       </c>
@@ -9353,7 +9368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>12</v>
       </c>
@@ -9385,7 +9400,7 @@
         <v>23773</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>12</v>
       </c>
@@ -9421,7 +9436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>12</v>
       </c>
@@ -9453,7 +9468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>12</v>
       </c>
@@ -9485,7 +9500,7 @@
         <v>545953</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>12</v>
       </c>
@@ -9517,7 +9532,7 @@
         <v>962122</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>12</v>
       </c>
@@ -9554,7 +9569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>12</v>
       </c>
@@ -9586,7 +9601,7 @@
         <v>88455</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>12</v>
       </c>
@@ -9618,7 +9633,7 @@
         <v>253372</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>12</v>
       </c>
@@ -9655,7 +9670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>12</v>
       </c>
@@ -9692,7 +9707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>12</v>
       </c>
@@ -9726,7 +9741,7 @@
         <v>8820</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>12</v>
       </c>
@@ -9760,7 +9775,7 @@
         <v>5280</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>12</v>
       </c>
@@ -9796,7 +9811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>12</v>
       </c>
@@ -9823,7 +9838,7 @@
         <v>1561940</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>12</v>
       </c>
@@ -9850,7 +9865,7 @@
         <v>1785250</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>12</v>
       </c>
@@ -9886,7 +9901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>12</v>
       </c>
@@ -9922,7 +9937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>12</v>
       </c>
@@ -9959,7 +9974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>12</v>
       </c>
@@ -9974,7 +9989,7 @@
       </c>
       <c r="G277" s="9"/>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>12</v>
       </c>
@@ -10010,7 +10025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>12</v>
       </c>
@@ -10045,7 +10060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>12</v>
       </c>
@@ -10080,7 +10095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>12</v>
       </c>
@@ -10115,7 +10130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>12</v>
       </c>
@@ -10151,7 +10166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>12</v>
       </c>
@@ -10188,7 +10203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>12</v>
       </c>
@@ -10221,7 +10236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>12</v>
       </c>
@@ -10257,7 +10272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>12</v>
       </c>
@@ -10289,7 +10304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>12</v>
       </c>
@@ -10322,7 +10337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>12</v>
       </c>
@@ -10355,7 +10370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>12</v>
       </c>
@@ -10391,7 +10406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>12</v>
       </c>
@@ -10424,7 +10439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>12</v>
       </c>
@@ -10456,7 +10471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>12</v>
       </c>
@@ -10488,7 +10503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>12</v>
       </c>
@@ -10524,7 +10539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>12</v>
       </c>
@@ -10557,7 +10572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>12</v>
       </c>
@@ -10593,7 +10608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>12</v>
       </c>
@@ -10625,7 +10640,7 @@
         <v>2099030</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>12</v>
       </c>
@@ -10657,7 +10672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>12</v>
       </c>
@@ -10689,7 +10704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>12</v>
       </c>
@@ -10725,7 +10740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>12</v>
       </c>
@@ -10758,7 +10773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>12</v>
       </c>
@@ -10794,7 +10809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>12</v>
       </c>
@@ -10827,7 +10842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>12</v>
       </c>
@@ -10863,7 +10878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>12</v>
       </c>
@@ -10899,7 +10914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>12</v>
       </c>
@@ -10928,7 +10943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>12</v>
       </c>
@@ -10963,7 +10978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>12</v>
       </c>
@@ -10996,7 +11011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>12</v>
       </c>
@@ -11032,7 +11047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>12</v>
       </c>
@@ -11068,7 +11083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>12</v>
       </c>
@@ -11104,7 +11119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>12</v>
       </c>
@@ -11140,7 +11155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>12</v>
       </c>
@@ -11177,7 +11192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>12</v>
       </c>
@@ -11213,7 +11228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>12</v>
       </c>
@@ -11254,9 +11269,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33CA0F3-68C3-4F60-B516-F4CB80D1245F}">
   <dimension ref="A1:H49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11282,17 +11297,17 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1976</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1977</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1978</v>
       </c>
@@ -11309,7 +11324,7 @@
         <v>1.5980000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1979</v>
       </c>
@@ -11326,7 +11341,7 @@
         <v>0.76800000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1980</v>
       </c>
@@ -11349,7 +11364,7 @@
         <v>4.6239999999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1981</v>
       </c>
@@ -11375,7 +11390,7 @@
         <v>2.8769999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1982</v>
       </c>
@@ -11401,7 +11416,7 @@
         <v>2.145</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1983</v>
       </c>
@@ -11427,7 +11442,7 @@
         <v>3.7850000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1984</v>
       </c>
@@ -11453,7 +11468,7 @@
         <v>4.298</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1985</v>
       </c>
@@ -11479,7 +11494,7 @@
         <v>3.512</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1986</v>
       </c>
@@ -11505,7 +11520,7 @@
         <v>4.2549999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1987</v>
       </c>
@@ -11531,7 +11546,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1988</v>
       </c>
@@ -11557,7 +11572,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1989</v>
       </c>
@@ -11583,7 +11598,7 @@
         <v>2.0670000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1990</v>
       </c>
@@ -11609,7 +11624,7 @@
         <v>2.5710000000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1991</v>
       </c>
@@ -11635,7 +11650,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1992</v>
       </c>
@@ -11661,7 +11676,7 @@
         <v>0.85899999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1993</v>
       </c>
@@ -11687,7 +11702,7 @@
         <v>0.94699999999999995</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1994</v>
       </c>
@@ -11713,7 +11728,7 @@
         <v>0.89900000000000002</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1995</v>
       </c>
@@ -11739,7 +11754,7 @@
         <v>5.4619999999999997</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1996</v>
       </c>
@@ -11765,7 +11780,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1997</v>
       </c>
@@ -11791,7 +11806,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1998</v>
       </c>
@@ -11817,7 +11832,7 @@
         <v>1.9650000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1999</v>
       </c>
@@ -11843,7 +11858,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2000</v>
       </c>
@@ -11869,7 +11884,7 @@
         <v>2.0579999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2001</v>
       </c>
@@ -11895,7 +11910,7 @@
         <v>1.0660000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2002</v>
       </c>
@@ -11921,7 +11936,7 @@
         <v>2.1360000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2003</v>
       </c>
@@ -11947,7 +11962,7 @@
         <v>1.8240000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>2004</v>
       </c>
@@ -11973,7 +11988,7 @@
         <v>1.367</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>2005</v>
       </c>
@@ -11999,7 +12014,7 @@
         <v>1.2270000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>2006</v>
       </c>
@@ -12025,7 +12040,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>2007</v>
       </c>
@@ -12051,7 +12066,7 @@
         <v>0.63400000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>2008</v>
       </c>
@@ -12077,7 +12092,7 @@
         <v>0.48199999999999998</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>2009</v>
       </c>
@@ -12103,7 +12118,7 @@
         <v>1.7568999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>2010</v>
       </c>
@@ -12129,7 +12144,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>2011</v>
       </c>
@@ -12155,7 +12170,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>2012</v>
       </c>
@@ -12181,7 +12196,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>2013</v>
       </c>
@@ -12207,7 +12222,7 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>2014</v>
       </c>
@@ -12227,7 +12242,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>2015</v>
       </c>
@@ -12241,7 +12256,7 @@
         <v>0.61099999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>2016</v>
       </c>
@@ -12252,7 +12267,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>2017</v>
       </c>
@@ -12263,7 +12278,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>2018</v>
       </c>
@@ -12274,7 +12289,7 @@
         <v>5.73</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>2019</v>
       </c>
@@ -12285,7 +12300,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>2020</v>
       </c>
@@ -12296,7 +12311,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>2021</v>
       </c>
@@ -12307,7 +12322,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>2022</v>
       </c>
@@ -12318,7 +12333,7 @@
         <v>2.2079209999999998</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>2023</v>
       </c>
